--- a/projetos/relatorio-macro-excel/relatorio_macro.xlsx
+++ b/projetos/relatorio-macro-excel/relatorio_macro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Câmbio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPCA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Câmbio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IPCA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -221,14 +221,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -251,7 +251,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="E85D04"/>
               </a:solidFill>
@@ -261,19 +261,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Selic'!$A$5:$A$190</f>
+              <f>'Selic'!$A$5:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Selic'!$B$5:$B$190</f>
+              <f>'Selic'!$B$5:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -309,14 +309,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -339,7 +339,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="E85D04"/>
               </a:solidFill>
@@ -349,7 +349,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -397,14 +397,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -427,7 +427,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="E85D04"/>
               </a:solidFill>
@@ -437,7 +437,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -485,7 +485,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -500,9 +500,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -512,7 +512,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -527,9 +527,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -539,7 +539,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -554,9 +554,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -894,7 +894,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 16/07/2026 19:08 · Fonte: Banco Central do Brasil (API SGS)</t>
+          <t>Gerado automaticamente em 01/08/2026 13:41 · Fonte: Banco Central do Brasil (API SGS)</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>14,40% a.a.</t>
+          <t>14,15% a.a.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>em 2026-06</t>
+          <t>em 2026-07</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2873,7 +2873,17 @@
         </is>
       </c>
       <c r="B190" s="14" t="n">
-        <v>14.4</v>
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="n">
+        <v>14.15</v>
       </c>
     </row>
   </sheetData>

--- a/projetos/relatorio-macro-excel/relatorio_macro.xlsx
+++ b/projetos/relatorio-macro-excel/relatorio_macro.xlsx
@@ -268,12 +268,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Selic'!$A$5:$A$191</f>
+              <f>'Selic'!$A$5:$A$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Selic'!$B$5:$B$191</f>
+              <f>'Selic'!$B$5:$B$192</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +356,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Câmbio'!$A$5:$A$190</f>
+              <f>'Câmbio'!$A$5:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Câmbio'!$B$5:$B$190</f>
+              <f>'Câmbio'!$B$5:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IPCA'!$A$5:$A$190</f>
+              <f>'IPCA'!$A$5:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IPCA'!$B$5:$B$190</f>
+              <f>'IPCA'!$B$5:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -894,7 +894,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 01/08/2026 13:41 · Fonte: Banco Central do Brasil (API SGS)</t>
+          <t>Gerado automaticamente em 01/09/2026 16:25 · Fonte: Banco Central do Brasil (API SGS)</t>
         </is>
       </c>
     </row>
@@ -923,44 +923,44 @@
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>14,15% a.a.</t>
+          <t>13,94% a.a.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>R$ 5,1276</t>
+          <t>R$ 5,1139</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,07%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>em 2026-08</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>em 2026-07</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>em 2026-06</t>
-        </is>
-      </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>até 2026-06</t>
+          <t>até 2026-07</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>em 2026-06</t>
+          <t>em 2026-07</t>
         </is>
       </c>
     </row>
@@ -978,6 +978,1931 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B192"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Taxa Selic (% a.a.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Fonte: Banco Central do Brasil — API SGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>11.91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2012-01</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>13.17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n">
+        <v>12.51</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="n">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="n">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="n">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="n">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B172" s="14" t="n">
+        <v>11.77</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="n">
+        <v>12.24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B174" s="14" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="n">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B176" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="n">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B178" s="14" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B180" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B182" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B184" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B185" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B186" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B188" s="14" t="n">
+        <v>14.64</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B190" s="14" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B192" s="14" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -993,7 +2918,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Taxa Selic (% a.a.)</t>
+          <t>Dólar — média mensal de venda (R$/US$)</t>
         </is>
       </c>
     </row>
@@ -1022,8 +2947,8 @@
           <t>2011-01</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>10.85</v>
+      <c r="B5" s="15" t="n">
+        <v>1.6749</v>
       </c>
     </row>
     <row r="6">
@@ -1032,8 +2957,8 @@
           <t>2011-02</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>11.17</v>
+      <c r="B6" s="16" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="7">
@@ -1042,8 +2967,8 @@
           <t>2011-03</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>11.62</v>
+      <c r="B7" s="15" t="n">
+        <v>1.6591</v>
       </c>
     </row>
     <row r="8">
@@ -1052,8 +2977,8 @@
           <t>2011-04</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>11.74</v>
+      <c r="B8" s="16" t="n">
+        <v>1.5864</v>
       </c>
     </row>
     <row r="9">
@@ -1062,8 +2987,8 @@
           <t>2011-05</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>11.92</v>
+      <c r="B9" s="15" t="n">
+        <v>1.6135</v>
       </c>
     </row>
     <row r="10">
@@ -1072,8 +2997,8 @@
           <t>2011-06</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>12.1</v>
+      <c r="B10" s="16" t="n">
+        <v>1.587</v>
       </c>
     </row>
     <row r="11">
@@ -1082,8 +3007,8 @@
           <t>2011-07</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>12.25</v>
+      <c r="B11" s="15" t="n">
+        <v>1.5639</v>
       </c>
     </row>
     <row r="12">
@@ -1092,8 +3017,8 @@
           <t>2011-08</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>12.42</v>
+      <c r="B12" s="16" t="n">
+        <v>1.597</v>
       </c>
     </row>
     <row r="13">
@@ -1102,8 +3027,8 @@
           <t>2011-09</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>11.91</v>
+      <c r="B13" s="15" t="n">
+        <v>1.7498</v>
       </c>
     </row>
     <row r="14">
@@ -1112,8 +3037,8 @@
           <t>2011-10</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>11.7</v>
+      <c r="B14" s="16" t="n">
+        <v>1.7726</v>
       </c>
     </row>
     <row r="15">
@@ -1122,8 +3047,8 @@
           <t>2011-11</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>11.4</v>
+      <c r="B15" s="15" t="n">
+        <v>1.7905</v>
       </c>
     </row>
     <row r="16">
@@ -1132,8 +3057,8 @@
           <t>2011-12</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>10.9</v>
+      <c r="B16" s="16" t="n">
+        <v>1.8369</v>
       </c>
     </row>
     <row r="17">
@@ -1142,8 +3067,8 @@
           <t>2012-01</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>10.7</v>
+      <c r="B17" s="15" t="n">
+        <v>1.7897</v>
       </c>
     </row>
     <row r="18">
@@ -1152,8 +3077,8 @@
           <t>2012-02</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>10.4</v>
+      <c r="B18" s="16" t="n">
+        <v>1.7184</v>
       </c>
     </row>
     <row r="19">
@@ -1162,8 +3087,8 @@
           <t>2012-03</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>9.82</v>
+      <c r="B19" s="15" t="n">
+        <v>1.7953</v>
       </c>
     </row>
     <row r="20">
@@ -1172,8 +3097,8 @@
           <t>2012-04</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>9.35</v>
+      <c r="B20" s="16" t="n">
+        <v>1.8548</v>
       </c>
     </row>
     <row r="21">
@@ -1182,8 +3107,8 @@
           <t>2012-05</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>8.869999999999999</v>
+      <c r="B21" s="15" t="n">
+        <v>1.986</v>
       </c>
     </row>
     <row r="22">
@@ -1192,8 +3117,8 @@
           <t>2012-06</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>8.390000000000001</v>
+      <c r="B22" s="16" t="n">
+        <v>2.0492</v>
       </c>
     </row>
     <row r="23">
@@ -1202,8 +3127,8 @@
           <t>2012-07</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>8.07</v>
+      <c r="B23" s="15" t="n">
+        <v>2.0287</v>
       </c>
     </row>
     <row r="24">
@@ -1212,8 +3137,8 @@
           <t>2012-08</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>7.85</v>
+      <c r="B24" s="16" t="n">
+        <v>2.0294</v>
       </c>
     </row>
     <row r="25">
@@ -1222,8 +3147,8 @@
           <t>2012-09</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>7.39</v>
+      <c r="B25" s="15" t="n">
+        <v>2.0281</v>
       </c>
     </row>
     <row r="26">
@@ -1232,8 +3157,8 @@
           <t>2012-10</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>7.23</v>
+      <c r="B26" s="16" t="n">
+        <v>2.0298</v>
       </c>
     </row>
     <row r="27">
@@ -1242,8 +3167,8 @@
           <t>2012-11</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>7.14</v>
+      <c r="B27" s="15" t="n">
+        <v>2.0678</v>
       </c>
     </row>
     <row r="28">
@@ -1252,8 +3177,8 @@
           <t>2012-12</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>7.16</v>
+      <c r="B28" s="16" t="n">
+        <v>2.0778</v>
       </c>
     </row>
     <row r="29">
@@ -1262,8 +3187,8 @@
           <t>2013-01</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
-        <v>7.11</v>
+      <c r="B29" s="15" t="n">
+        <v>2.0311</v>
       </c>
     </row>
     <row r="30">
@@ -1272,8 +3197,8 @@
           <t>2013-02</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>7.12</v>
+      <c r="B30" s="16" t="n">
+        <v>1.9733</v>
       </c>
     </row>
     <row r="31">
@@ -1282,8 +3207,8 @@
           <t>2013-03</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>7.15</v>
+      <c r="B31" s="15" t="n">
+        <v>1.9828</v>
       </c>
     </row>
     <row r="32">
@@ -1292,8 +3217,8 @@
           <t>2013-04</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>7.26</v>
+      <c r="B32" s="16" t="n">
+        <v>2.0022</v>
       </c>
     </row>
     <row r="33">
@@ -1302,8 +3227,8 @@
           <t>2013-05</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>7.42</v>
+      <c r="B33" s="15" t="n">
+        <v>2.0348</v>
       </c>
     </row>
     <row r="34">
@@ -1312,8 +3237,8 @@
           <t>2013-06</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>7.9</v>
+      <c r="B34" s="16" t="n">
+        <v>2.173</v>
       </c>
     </row>
     <row r="35">
@@ -1322,8 +3247,8 @@
           <t>2013-07</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>8.23</v>
+      <c r="B35" s="15" t="n">
+        <v>2.2522</v>
       </c>
     </row>
     <row r="36">
@@ -1332,8 +3257,8 @@
           <t>2013-08</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v>8.449999999999999</v>
+      <c r="B36" s="16" t="n">
+        <v>2.3422</v>
       </c>
     </row>
     <row r="37">
@@ -1342,8 +3267,8 @@
           <t>2013-09</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
-        <v>8.9</v>
+      <c r="B37" s="15" t="n">
+        <v>2.2705</v>
       </c>
     </row>
     <row r="38">
@@ -1352,8 +3277,8 @@
           <t>2013-10</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>9.25</v>
+      <c r="B38" s="16" t="n">
+        <v>2.1886</v>
       </c>
     </row>
     <row r="39">
@@ -1362,8 +3287,8 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
-        <v>9.449999999999999</v>
+      <c r="B39" s="15" t="n">
+        <v>2.2954</v>
       </c>
     </row>
     <row r="40">
@@ -1372,8 +3297,8 @@
           <t>2013-12</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v>9.9</v>
+      <c r="B40" s="16" t="n">
+        <v>2.3455</v>
       </c>
     </row>
     <row r="41">
@@ -1382,8 +3307,8 @@
           <t>2014-01</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
-        <v>10.17</v>
+      <c r="B41" s="15" t="n">
+        <v>2.3822</v>
       </c>
     </row>
     <row r="42">
@@ -1392,8 +3317,8 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>10.43</v>
+      <c r="B42" s="16" t="n">
+        <v>2.3837</v>
       </c>
     </row>
     <row r="43">
@@ -1402,8 +3327,8 @@
           <t>2014-03</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
-        <v>10.65</v>
+      <c r="B43" s="15" t="n">
+        <v>2.3261</v>
       </c>
     </row>
     <row r="44">
@@ -1412,8 +3337,8 @@
           <t>2014-04</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
-        <v>10.87</v>
+      <c r="B44" s="16" t="n">
+        <v>2.2328</v>
       </c>
     </row>
     <row r="45">
@@ -1422,8 +3347,8 @@
           <t>2014-05</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n">
-        <v>10.9</v>
+      <c r="B45" s="15" t="n">
+        <v>2.2209</v>
       </c>
     </row>
     <row r="46">
@@ -1432,8 +3357,8 @@
           <t>2014-06</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
-        <v>10.9</v>
+      <c r="B46" s="16" t="n">
+        <v>2.2355</v>
       </c>
     </row>
     <row r="47">
@@ -1442,8 +3367,8 @@
           <t>2014-07</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
-        <v>10.9</v>
+      <c r="B47" s="15" t="n">
+        <v>2.2246</v>
       </c>
     </row>
     <row r="48">
@@ -1452,8 +3377,8 @@
           <t>2014-08</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n">
-        <v>10.9</v>
+      <c r="B48" s="16" t="n">
+        <v>2.268</v>
       </c>
     </row>
     <row r="49">
@@ -1462,8 +3387,8 @@
           <t>2014-09</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
-        <v>10.9</v>
+      <c r="B49" s="15" t="n">
+        <v>2.3329</v>
       </c>
     </row>
     <row r="50">
@@ -1472,8 +3397,8 @@
           <t>2014-10</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
-        <v>10.92</v>
+      <c r="B50" s="16" t="n">
+        <v>2.4483</v>
       </c>
     </row>
     <row r="51">
@@ -1482,8 +3407,8 @@
           <t>2014-11</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
-        <v>11.15</v>
+      <c r="B51" s="15" t="n">
+        <v>2.5484</v>
       </c>
     </row>
     <row r="52">
@@ -1492,8 +3417,8 @@
           <t>2014-12</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
-        <v>11.58</v>
+      <c r="B52" s="16" t="n">
+        <v>2.6394</v>
       </c>
     </row>
     <row r="53">
@@ -1502,8 +3427,8 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
-        <v>11.82</v>
+      <c r="B53" s="15" t="n">
+        <v>2.6342</v>
       </c>
     </row>
     <row r="54">
@@ -1512,8 +3437,8 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="B54" s="14" t="n">
-        <v>12.15</v>
+      <c r="B54" s="16" t="n">
+        <v>2.8165</v>
       </c>
     </row>
     <row r="55">
@@ -1522,8 +3447,8 @@
           <t>2015-03</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n">
-        <v>12.58</v>
+      <c r="B55" s="15" t="n">
+        <v>3.1395</v>
       </c>
     </row>
     <row r="56">
@@ -1532,8 +3457,8 @@
           <t>2015-04</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
-        <v>12.68</v>
+      <c r="B56" s="16" t="n">
+        <v>3.0432</v>
       </c>
     </row>
     <row r="57">
@@ -1542,8 +3467,8 @@
           <t>2015-05</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
-        <v>13.15</v>
+      <c r="B57" s="15" t="n">
+        <v>3.0617</v>
       </c>
     </row>
     <row r="58">
@@ -1552,8 +3477,8 @@
           <t>2015-06</t>
         </is>
       </c>
-      <c r="B58" s="14" t="n">
-        <v>13.58</v>
+      <c r="B58" s="16" t="n">
+        <v>3.1117</v>
       </c>
     </row>
     <row r="59">
@@ -1562,8 +3487,8 @@
           <t>2015-07</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n">
-        <v>13.69</v>
+      <c r="B59" s="15" t="n">
+        <v>3.2231</v>
       </c>
     </row>
     <row r="60">
@@ -1572,8 +3497,8 @@
           <t>2015-08</t>
         </is>
       </c>
-      <c r="B60" s="14" t="n">
-        <v>14.15</v>
+      <c r="B60" s="16" t="n">
+        <v>3.5143</v>
       </c>
     </row>
     <row r="61">
@@ -1582,8 +3507,8 @@
           <t>2015-09</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
-        <v>14.15</v>
+      <c r="B61" s="15" t="n">
+        <v>3.9065</v>
       </c>
     </row>
     <row r="62">
@@ -1592,8 +3517,8 @@
           <t>2015-10</t>
         </is>
       </c>
-      <c r="B62" s="14" t="n">
-        <v>14.15</v>
+      <c r="B62" s="16" t="n">
+        <v>3.8801</v>
       </c>
     </row>
     <row r="63">
@@ -1602,8 +3527,8 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n">
-        <v>14.15</v>
+      <c r="B63" s="15" t="n">
+        <v>3.7765</v>
       </c>
     </row>
     <row r="64">
@@ -1612,8 +3537,8 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="B64" s="14" t="n">
-        <v>14.15</v>
+      <c r="B64" s="16" t="n">
+        <v>3.8711</v>
       </c>
     </row>
     <row r="65">
@@ -1622,8 +3547,8 @@
           <t>2016-01</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
-        <v>14.15</v>
+      <c r="B65" s="15" t="n">
+        <v>4.0524</v>
       </c>
     </row>
     <row r="66">
@@ -1632,8 +3557,8 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
-        <v>14.15</v>
+      <c r="B66" s="16" t="n">
+        <v>3.9737</v>
       </c>
     </row>
     <row r="67">
@@ -1642,8 +3567,8 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n">
-        <v>14.15</v>
+      <c r="B67" s="15" t="n">
+        <v>3.7039</v>
       </c>
     </row>
     <row r="68">
@@ -1652,8 +3577,8 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
-        <v>14.15</v>
+      <c r="B68" s="16" t="n">
+        <v>3.5658</v>
       </c>
     </row>
     <row r="69">
@@ -1662,8 +3587,8 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n">
-        <v>14.15</v>
+      <c r="B69" s="15" t="n">
+        <v>3.5393</v>
       </c>
     </row>
     <row r="70">
@@ -1672,8 +3597,8 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
-        <v>14.15</v>
+      <c r="B70" s="16" t="n">
+        <v>3.4245</v>
       </c>
     </row>
     <row r="71">
@@ -1682,8 +3607,8 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="B71" s="12" t="n">
-        <v>14.15</v>
+      <c r="B71" s="15" t="n">
+        <v>3.2756</v>
       </c>
     </row>
     <row r="72">
@@ -1692,8 +3617,8 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="B72" s="14" t="n">
-        <v>14.15</v>
+      <c r="B72" s="16" t="n">
+        <v>3.2097</v>
       </c>
     </row>
     <row r="73">
@@ -1702,8 +3627,8 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
-        <v>14.15</v>
+      <c r="B73" s="15" t="n">
+        <v>3.2564</v>
       </c>
     </row>
     <row r="74">
@@ -1712,8 +3637,8 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="B74" s="14" t="n">
-        <v>14.05</v>
+      <c r="B74" s="16" t="n">
+        <v>3.1858</v>
       </c>
     </row>
     <row r="75">
@@ -1722,8 +3647,8 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
-        <v>13.9</v>
+      <c r="B75" s="15" t="n">
+        <v>3.342</v>
       </c>
     </row>
     <row r="76">
@@ -1732,8 +3657,8 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="B76" s="14" t="n">
-        <v>13.65</v>
+      <c r="B76" s="16" t="n">
+        <v>3.3523</v>
       </c>
     </row>
     <row r="77">
@@ -1742,8 +3667,8 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n">
-        <v>13.17</v>
+      <c r="B77" s="15" t="n">
+        <v>3.1966</v>
       </c>
     </row>
     <row r="78">
@@ -1752,8 +3677,8 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="B78" s="14" t="n">
-        <v>12.82</v>
+      <c r="B78" s="16" t="n">
+        <v>3.1042</v>
       </c>
     </row>
     <row r="79">
@@ -1762,8 +3687,8 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n">
-        <v>12.15</v>
+      <c r="B79" s="15" t="n">
+        <v>3.1279</v>
       </c>
     </row>
     <row r="80">
@@ -1772,8 +3697,8 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="B80" s="14" t="n">
-        <v>11.59</v>
+      <c r="B80" s="16" t="n">
+        <v>3.1362</v>
       </c>
     </row>
     <row r="81">
@@ -1782,8 +3707,8 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n">
-        <v>11.15</v>
+      <c r="B81" s="15" t="n">
+        <v>3.2095</v>
       </c>
     </row>
     <row r="82">
@@ -1792,8 +3717,8 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="B82" s="14" t="n">
-        <v>10.15</v>
+      <c r="B82" s="16" t="n">
+        <v>3.2954</v>
       </c>
     </row>
     <row r="83">
@@ -1802,8 +3727,8 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n">
-        <v>10.01</v>
+      <c r="B83" s="15" t="n">
+        <v>3.2061</v>
       </c>
     </row>
     <row r="84">
@@ -1812,8 +3737,8 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="B84" s="14" t="n">
-        <v>9.15</v>
+      <c r="B84" s="16" t="n">
+        <v>3.1509</v>
       </c>
     </row>
     <row r="85">
@@ -1822,8 +3747,8 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n">
-        <v>8.35</v>
+      <c r="B85" s="15" t="n">
+        <v>3.1348</v>
       </c>
     </row>
     <row r="86">
@@ -1832,8 +3757,8 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="B86" s="14" t="n">
-        <v>8.01</v>
+      <c r="B86" s="16" t="n">
+        <v>3.1912</v>
       </c>
     </row>
     <row r="87">
@@ -1842,8 +3767,8 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="B87" s="12" t="n">
-        <v>7.4</v>
+      <c r="B87" s="15" t="n">
+        <v>3.2594</v>
       </c>
     </row>
     <row r="88">
@@ -1852,8 +3777,8 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="B88" s="14" t="n">
-        <v>7</v>
+      <c r="B88" s="16" t="n">
+        <v>3.2919</v>
       </c>
     </row>
     <row r="89">
@@ -1862,8 +3787,8 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="B89" s="12" t="n">
-        <v>6.9</v>
+      <c r="B89" s="15" t="n">
+        <v>3.2106</v>
       </c>
     </row>
     <row r="90">
@@ -1872,8 +3797,8 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="B90" s="14" t="n">
-        <v>6.72</v>
+      <c r="B90" s="16" t="n">
+        <v>3.2415</v>
       </c>
     </row>
     <row r="91">
@@ -1882,8 +3807,8 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="B91" s="12" t="n">
-        <v>6.58</v>
+      <c r="B91" s="15" t="n">
+        <v>3.2792</v>
       </c>
     </row>
     <row r="92">
@@ -1892,8 +3817,8 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n">
-        <v>6.4</v>
+      <c r="B92" s="16" t="n">
+        <v>3.4075</v>
       </c>
     </row>
     <row r="93">
@@ -1902,8 +3827,8 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="B93" s="12" t="n">
-        <v>6.4</v>
+      <c r="B93" s="15" t="n">
+        <v>3.6361</v>
       </c>
     </row>
     <row r="94">
@@ -1912,8 +3837,8 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="B94" s="14" t="n">
-        <v>6.4</v>
+      <c r="B94" s="16" t="n">
+        <v>3.7732</v>
       </c>
     </row>
     <row r="95">
@@ -1922,8 +3847,8 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="B95" s="12" t="n">
-        <v>6.4</v>
+      <c r="B95" s="15" t="n">
+        <v>3.8288</v>
       </c>
     </row>
     <row r="96">
@@ -1932,8 +3857,8 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="B96" s="14" t="n">
-        <v>6.4</v>
+      <c r="B96" s="16" t="n">
+        <v>3.9298</v>
       </c>
     </row>
     <row r="97">
@@ -1942,8 +3867,8 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="B97" s="12" t="n">
-        <v>6.4</v>
+      <c r="B97" s="15" t="n">
+        <v>4.1165</v>
       </c>
     </row>
     <row r="98">
@@ -1952,8 +3877,8 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n">
-        <v>6.4</v>
+      <c r="B98" s="16" t="n">
+        <v>3.7584</v>
       </c>
     </row>
     <row r="99">
@@ -1962,8 +3887,8 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="B99" s="12" t="n">
-        <v>6.4</v>
+      <c r="B99" s="15" t="n">
+        <v>3.7867</v>
       </c>
     </row>
     <row r="100">
@@ -1972,8 +3897,8 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="B100" s="14" t="n">
-        <v>6.4</v>
+      <c r="B100" s="16" t="n">
+        <v>3.8851</v>
       </c>
     </row>
     <row r="101">
@@ -1982,8 +3907,8 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="B101" s="12" t="n">
-        <v>6.4</v>
+      <c r="B101" s="15" t="n">
+        <v>3.7417</v>
       </c>
     </row>
     <row r="102">
@@ -1992,8 +3917,8 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="B102" s="14" t="n">
-        <v>6.4</v>
+      <c r="B102" s="16" t="n">
+        <v>3.7236</v>
       </c>
     </row>
     <row r="103">
@@ -2002,8 +3927,8 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="B103" s="12" t="n">
-        <v>6.4</v>
+      <c r="B103" s="15" t="n">
+        <v>3.8465</v>
       </c>
     </row>
     <row r="104">
@@ -2012,8 +3937,8 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="B104" s="14" t="n">
-        <v>6.4</v>
+      <c r="B104" s="16" t="n">
+        <v>3.8962</v>
       </c>
     </row>
     <row r="105">
@@ -2022,8 +3947,8 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B105" s="12" t="n">
-        <v>6.4</v>
+      <c r="B105" s="15" t="n">
+        <v>4.0015</v>
       </c>
     </row>
     <row r="106">
@@ -2032,8 +3957,8 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
-        <v>6.4</v>
+      <c r="B106" s="16" t="n">
+        <v>3.8588</v>
       </c>
     </row>
     <row r="107">
@@ -2042,8 +3967,8 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B107" s="12" t="n">
-        <v>6.4</v>
+      <c r="B107" s="15" t="n">
+        <v>3.7793</v>
       </c>
     </row>
     <row r="108">
@@ -2052,8 +3977,8 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="B108" s="14" t="n">
-        <v>5.9</v>
+      <c r="B108" s="16" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="109">
@@ -2062,8 +3987,8 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B109" s="12" t="n">
-        <v>5.71</v>
+      <c r="B109" s="15" t="n">
+        <v>4.1215</v>
       </c>
     </row>
     <row r="110">
@@ -2072,8 +3997,8 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B110" s="14" t="n">
-        <v>5.38</v>
+      <c r="B110" s="16" t="n">
+        <v>4.087</v>
       </c>
     </row>
     <row r="111">
@@ -2082,8 +4007,8 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B111" s="12" t="n">
-        <v>4.9</v>
+      <c r="B111" s="15" t="n">
+        <v>4.1553</v>
       </c>
     </row>
     <row r="112">
@@ -2092,8 +4017,8 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="B112" s="14" t="n">
-        <v>4.59</v>
+      <c r="B112" s="16" t="n">
+        <v>4.1096</v>
       </c>
     </row>
     <row r="113">
@@ -2102,8 +4027,8 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B113" s="12" t="n">
-        <v>4.4</v>
+      <c r="B113" s="15" t="n">
+        <v>4.1495</v>
       </c>
     </row>
     <row r="114">
@@ -2112,8 +4037,8 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
-        <v>4.19</v>
+      <c r="B114" s="16" t="n">
+        <v>4.341</v>
       </c>
     </row>
     <row r="115">
@@ -2122,8 +4047,8 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B115" s="12" t="n">
-        <v>3.95</v>
+      <c r="B115" s="15" t="n">
+        <v>4.8839</v>
       </c>
     </row>
     <row r="116">
@@ -2132,8 +4057,8 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B116" s="14" t="n">
-        <v>3.65</v>
+      <c r="B116" s="16" t="n">
+        <v>5.3256</v>
       </c>
     </row>
     <row r="117">
@@ -2142,8 +4067,8 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B117" s="12" t="n">
-        <v>3.01</v>
+      <c r="B117" s="15" t="n">
+        <v>5.6434</v>
       </c>
     </row>
     <row r="118">
@@ -2152,8 +4077,8 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="B118" s="14" t="n">
-        <v>2.58</v>
+      <c r="B118" s="16" t="n">
+        <v>5.1966</v>
       </c>
     </row>
     <row r="119">
@@ -2162,8 +4087,8 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B119" s="12" t="n">
-        <v>2.15</v>
+      <c r="B119" s="15" t="n">
+        <v>5.2802</v>
       </c>
     </row>
     <row r="120">
@@ -2172,8 +4097,8 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B120" s="14" t="n">
-        <v>1.94</v>
+      <c r="B120" s="16" t="n">
+        <v>5.4612</v>
       </c>
     </row>
     <row r="121">
@@ -2182,8 +4107,8 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="B121" s="12" t="n">
-        <v>1.9</v>
+      <c r="B121" s="15" t="n">
+        <v>5.3995</v>
       </c>
     </row>
     <row r="122">
@@ -2192,8 +4117,8 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B122" s="14" t="n">
-        <v>1.9</v>
+      <c r="B122" s="16" t="n">
+        <v>5.6258</v>
       </c>
     </row>
     <row r="123">
@@ -2202,8 +4127,8 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B123" s="12" t="n">
-        <v>1.9</v>
+      <c r="B123" s="15" t="n">
+        <v>5.4178</v>
       </c>
     </row>
     <row r="124">
@@ -2212,8 +4137,8 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B124" s="14" t="n">
-        <v>1.9</v>
+      <c r="B124" s="16" t="n">
+        <v>5.1456</v>
       </c>
     </row>
     <row r="125">
@@ -2222,8 +4147,8 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B125" s="12" t="n">
-        <v>1.9</v>
+      <c r="B125" s="15" t="n">
+        <v>5.3562</v>
       </c>
     </row>
     <row r="126">
@@ -2232,8 +4157,8 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B126" s="14" t="n">
-        <v>1.9</v>
+      <c r="B126" s="16" t="n">
+        <v>5.4165</v>
       </c>
     </row>
     <row r="127">
@@ -2242,8 +4167,8 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B127" s="12" t="n">
-        <v>2.23</v>
+      <c r="B127" s="15" t="n">
+        <v>5.6461</v>
       </c>
     </row>
     <row r="128">
@@ -2252,8 +4177,8 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B128" s="14" t="n">
-        <v>2.65</v>
+      <c r="B128" s="16" t="n">
+        <v>5.5621</v>
       </c>
     </row>
     <row r="129">
@@ -2262,8 +4187,8 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B129" s="12" t="n">
-        <v>3.29</v>
+      <c r="B129" s="15" t="n">
+        <v>5.2911</v>
       </c>
     </row>
     <row r="130">
@@ -2272,8 +4197,8 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B130" s="14" t="n">
-        <v>3.76</v>
+      <c r="B130" s="16" t="n">
+        <v>5.0319</v>
       </c>
     </row>
     <row r="131">
@@ -2282,8 +4207,8 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="B131" s="12" t="n">
-        <v>4.15</v>
+      <c r="B131" s="15" t="n">
+        <v>5.1567</v>
       </c>
     </row>
     <row r="132">
@@ -2292,8 +4217,8 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B132" s="14" t="n">
-        <v>5.01</v>
+      <c r="B132" s="16" t="n">
+        <v>5.2517</v>
       </c>
     </row>
     <row r="133">
@@ -2302,8 +4227,8 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B133" s="12" t="n">
-        <v>5.43</v>
+      <c r="B133" s="15" t="n">
+        <v>5.2797</v>
       </c>
     </row>
     <row r="134">
@@ -2312,8 +4237,8 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B134" s="14" t="n">
-        <v>6.3</v>
+      <c r="B134" s="16" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="135">
@@ -2322,8 +4247,8 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B135" s="12" t="n">
-        <v>7.65</v>
+      <c r="B135" s="15" t="n">
+        <v>5.5569</v>
       </c>
     </row>
     <row r="136">
@@ -2332,8 +4257,8 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B136" s="14" t="n">
-        <v>8.76</v>
+      <c r="B136" s="16" t="n">
+        <v>5.6514</v>
       </c>
     </row>
     <row r="137">
@@ -2342,8 +4267,8 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B137" s="12" t="n">
-        <v>9.15</v>
+      <c r="B137" s="15" t="n">
+        <v>5.5341</v>
       </c>
     </row>
     <row r="138">
@@ -2352,8 +4277,8 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B138" s="14" t="n">
-        <v>10.49</v>
+      <c r="B138" s="16" t="n">
+        <v>5.1966</v>
       </c>
     </row>
     <row r="139">
@@ -2362,8 +4287,8 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="B139" s="12" t="n">
-        <v>11.15</v>
+      <c r="B139" s="15" t="n">
+        <v>4.9684</v>
       </c>
     </row>
     <row r="140">
@@ -2372,8 +4297,8 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="B140" s="14" t="n">
-        <v>11.65</v>
+      <c r="B140" s="16" t="n">
+        <v>4.758</v>
       </c>
     </row>
     <row r="141">
@@ -2382,8 +4307,8 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="B141" s="12" t="n">
-        <v>12.51</v>
+      <c r="B141" s="15" t="n">
+        <v>4.9551</v>
       </c>
     </row>
     <row r="142">
@@ -2392,8 +4317,8 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="B142" s="14" t="n">
-        <v>12.89</v>
+      <c r="B142" s="16" t="n">
+        <v>5.0492</v>
       </c>
     </row>
     <row r="143">
@@ -2402,8 +4327,8 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="B143" s="12" t="n">
-        <v>13.15</v>
+      <c r="B143" s="15" t="n">
+        <v>5.3681</v>
       </c>
     </row>
     <row r="144">
@@ -2412,8 +4337,8 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="B144" s="14" t="n">
-        <v>13.58</v>
+      <c r="B144" s="16" t="n">
+        <v>5.1433</v>
       </c>
     </row>
     <row r="145">
@@ -2422,8 +4347,8 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="B145" s="12" t="n">
-        <v>13.65</v>
+      <c r="B145" s="15" t="n">
+        <v>5.237</v>
       </c>
     </row>
     <row r="146">
@@ -2432,8 +4357,8 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="B146" s="14" t="n">
-        <v>13.65</v>
+      <c r="B146" s="16" t="n">
+        <v>5.2503</v>
       </c>
     </row>
     <row r="147">
@@ -2442,8 +4367,8 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="B147" s="12" t="n">
-        <v>13.65</v>
+      <c r="B147" s="15" t="n">
+        <v>5.2747</v>
       </c>
     </row>
     <row r="148">
@@ -2452,8 +4377,8 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="B148" s="14" t="n">
-        <v>13.65</v>
+      <c r="B148" s="16" t="n">
+        <v>5.2424</v>
       </c>
     </row>
     <row r="149">
@@ -2462,8 +4387,8 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="B149" s="12" t="n">
-        <v>13.65</v>
+      <c r="B149" s="15" t="n">
+        <v>5.2007</v>
       </c>
     </row>
     <row r="150">
@@ -2472,8 +4397,8 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="B150" s="14" t="n">
-        <v>13.65</v>
+      <c r="B150" s="16" t="n">
+        <v>5.1717</v>
       </c>
     </row>
     <row r="151">
@@ -2482,8 +4407,8 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="B151" s="12" t="n">
-        <v>13.65</v>
+      <c r="B151" s="15" t="n">
+        <v>5.2115</v>
       </c>
     </row>
     <row r="152">
@@ -2492,8 +4417,8 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="B152" s="14" t="n">
-        <v>13.65</v>
+      <c r="B152" s="16" t="n">
+        <v>5.0197</v>
       </c>
     </row>
     <row r="153">
@@ -2502,8 +4427,8 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="B153" s="12" t="n">
-        <v>13.65</v>
+      <c r="B153" s="15" t="n">
+        <v>4.9828</v>
       </c>
     </row>
     <row r="154">
@@ -2512,8 +4437,8 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="B154" s="14" t="n">
-        <v>13.65</v>
+      <c r="B154" s="16" t="n">
+        <v>4.8516</v>
       </c>
     </row>
     <row r="155">
@@ -2522,8 +4447,8 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="B155" s="12" t="n">
-        <v>13.65</v>
+      <c r="B155" s="15" t="n">
+        <v>4.8008</v>
       </c>
     </row>
     <row r="156">
@@ -2532,8 +4457,8 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="B156" s="14" t="n">
-        <v>13.19</v>
+      <c r="B156" s="16" t="n">
+        <v>4.9035</v>
       </c>
     </row>
     <row r="157">
@@ -2542,8 +4467,8 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="B157" s="12" t="n">
-        <v>12.97</v>
+      <c r="B157" s="15" t="n">
+        <v>4.937</v>
       </c>
     </row>
     <row r="158">
@@ -2552,8 +4477,8 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="B158" s="14" t="n">
-        <v>12.65</v>
+      <c r="B158" s="16" t="n">
+        <v>5.0648</v>
       </c>
     </row>
     <row r="159">
@@ -2562,8 +4487,8 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="B159" s="12" t="n">
-        <v>12.17</v>
+      <c r="B159" s="15" t="n">
+        <v>4.8983</v>
       </c>
     </row>
     <row r="160">
@@ -2572,8 +4497,8 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="B160" s="14" t="n">
-        <v>11.87</v>
+      <c r="B160" s="16" t="n">
+        <v>4.8972</v>
       </c>
     </row>
     <row r="161">
@@ -2582,8 +4507,8 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="B161" s="12" t="n">
-        <v>11.65</v>
+      <c r="B161" s="15" t="n">
+        <v>4.9144</v>
       </c>
     </row>
     <row r="162">
@@ -2592,8 +4517,8 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="B162" s="14" t="n">
-        <v>11.15</v>
+      <c r="B162" s="16" t="n">
+        <v>4.9644</v>
       </c>
     </row>
     <row r="163">
@@ -2602,8 +4527,8 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="B163" s="12" t="n">
-        <v>11</v>
+      <c r="B163" s="15" t="n">
+        <v>4.9801</v>
       </c>
     </row>
     <row r="164">
@@ -2612,8 +4537,8 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="B164" s="14" t="n">
-        <v>10.65</v>
+      <c r="B164" s="16" t="n">
+        <v>5.1291</v>
       </c>
     </row>
     <row r="165">
@@ -2622,8 +4547,8 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="B165" s="12" t="n">
-        <v>10.46</v>
+      <c r="B165" s="15" t="n">
+        <v>5.133</v>
       </c>
     </row>
     <row r="166">
@@ -2632,8 +4557,8 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="B166" s="14" t="n">
-        <v>10.4</v>
+      <c r="B166" s="16" t="n">
+        <v>5.389</v>
       </c>
     </row>
     <row r="167">
@@ -2642,8 +4567,8 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="B167" s="12" t="n">
-        <v>10.4</v>
+      <c r="B167" s="15" t="n">
+        <v>5.542</v>
       </c>
     </row>
     <row r="168">
@@ -2652,8 +4577,8 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="B168" s="14" t="n">
-        <v>10.4</v>
+      <c r="B168" s="16" t="n">
+        <v>5.5526</v>
       </c>
     </row>
     <row r="169">
@@ -2662,8 +4587,8 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B169" s="12" t="n">
-        <v>10.5</v>
+      <c r="B169" s="15" t="n">
+        <v>5.5416</v>
       </c>
     </row>
     <row r="170">
@@ -2672,8 +4597,8 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="B170" s="14" t="n">
-        <v>10.65</v>
+      <c r="B170" s="16" t="n">
+        <v>5.6241</v>
       </c>
     </row>
     <row r="171">
@@ -2682,8 +4607,8 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="B171" s="12" t="n">
-        <v>11.04</v>
+      <c r="B171" s="15" t="n">
+        <v>5.8071</v>
       </c>
     </row>
     <row r="172">
@@ -2692,8 +4617,8 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="B172" s="14" t="n">
-        <v>11.77</v>
+      <c r="B172" s="16" t="n">
+        <v>6.097</v>
       </c>
     </row>
     <row r="173">
@@ -2702,8 +4627,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B173" s="12" t="n">
-        <v>12.24</v>
+      <c r="B173" s="15" t="n">
+        <v>6.0218</v>
       </c>
     </row>
     <row r="174">
@@ -2712,8 +4637,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B174" s="14" t="n">
-        <v>13.15</v>
+      <c r="B174" s="16" t="n">
+        <v>5.7656</v>
       </c>
     </row>
     <row r="175">
@@ -2722,8 +4647,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B175" s="12" t="n">
-        <v>13.57</v>
+      <c r="B175" s="15" t="n">
+        <v>5.7468</v>
       </c>
     </row>
     <row r="176">
@@ -2732,8 +4657,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B176" s="14" t="n">
-        <v>14.15</v>
+      <c r="B176" s="16" t="n">
+        <v>5.7837</v>
       </c>
     </row>
     <row r="177">
@@ -2742,8 +4667,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B177" s="12" t="n">
-        <v>14.55</v>
+      <c r="B177" s="15" t="n">
+        <v>5.6674</v>
       </c>
     </row>
     <row r="178">
@@ -2752,8 +4677,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B178" s="14" t="n">
-        <v>14.74</v>
+      <c r="B178" s="16" t="n">
+        <v>5.5471</v>
       </c>
     </row>
     <row r="179">
@@ -2762,8 +4687,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B179" s="12" t="n">
-        <v>14.9</v>
+      <c r="B179" s="15" t="n">
+        <v>5.5285</v>
       </c>
     </row>
     <row r="180">
@@ -2772,8 +4697,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B180" s="14" t="n">
-        <v>14.9</v>
+      <c r="B180" s="16" t="n">
+        <v>5.4469</v>
       </c>
     </row>
     <row r="181">
@@ -2782,8 +4707,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B181" s="12" t="n">
-        <v>14.9</v>
+      <c r="B181" s="15" t="n">
+        <v>5.3674</v>
       </c>
     </row>
     <row r="182">
@@ -2792,8 +4717,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B182" s="14" t="n">
-        <v>14.9</v>
+      <c r="B182" s="16" t="n">
+        <v>5.3855</v>
       </c>
     </row>
     <row r="183">
@@ -2802,8 +4727,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B183" s="12" t="n">
-        <v>14.9</v>
+      <c r="B183" s="15" t="n">
+        <v>5.3409</v>
       </c>
     </row>
     <row r="184">
@@ -2812,8 +4737,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B184" s="14" t="n">
-        <v>14.9</v>
+      <c r="B184" s="16" t="n">
+        <v>5.4531</v>
       </c>
     </row>
     <row r="185">
@@ -2822,8 +4747,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B185" s="12" t="n">
-        <v>14.9</v>
+      <c r="B185" s="15" t="n">
+        <v>5.338</v>
       </c>
     </row>
     <row r="186">
@@ -2832,8 +4757,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B186" s="14" t="n">
-        <v>14.9</v>
+      <c r="B186" s="16" t="n">
+        <v>5.2006</v>
       </c>
     </row>
     <row r="187">
@@ -2842,8 +4767,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B187" s="12" t="n">
-        <v>14.8</v>
+      <c r="B187" s="15" t="n">
+        <v>5.2316</v>
       </c>
     </row>
     <row r="188">
@@ -2852,8 +4777,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B188" s="14" t="n">
-        <v>14.64</v>
+      <c r="B188" s="16" t="n">
+        <v>5.0331</v>
       </c>
     </row>
     <row r="189">
@@ -2862,8 +4787,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B189" s="12" t="n">
-        <v>14.4</v>
+      <c r="B189" s="15" t="n">
+        <v>4.9837</v>
       </c>
     </row>
     <row r="190">
@@ -2872,8 +4797,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B190" s="14" t="n">
-        <v>14.29</v>
+      <c r="B190" s="16" t="n">
+        <v>5.1276</v>
       </c>
     </row>
     <row r="191">
@@ -2882,1913 +4807,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B191" s="12" t="n">
-        <v>14.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B190"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Dólar — média mensal de venda (R$/US$)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Fonte: Banco Central do Brasil — API SGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Mês</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>2011-01</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>1.6749</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>2011-02</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>1.668</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>2011-03</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>1.6591</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>2011-04</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>1.5864</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>2011-05</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>1.6135</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>2011-06</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>1.587</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>2011-07</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>1.5639</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2011-08</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>1.597</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2011-09</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>1.7498</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1.7726</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>2011-11</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>1.7905</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>1.8369</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>2012-01</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>1.7897</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>2012-02</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>1.7184</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>2012-03</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>1.7953</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>2012-04</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>1.8548</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>2012-05</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>1.986</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>2012-06</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>2.0492</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2012-07</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>2.0287</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>2012-08</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>2.0294</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>2012-09</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>2.0281</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>2012-10</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>2.0298</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>2012-11</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>2.0678</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>2012-12</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>2.0778</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>2013-01</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>2.0311</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>2013-02</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>1.9733</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>2013-03</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>1.9828</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>2.0022</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>2013-05</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>2.0348</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>2013-06</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
-        <v>2.173</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>2013-07</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>2.2522</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>2013-08</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>2.3422</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>2013-09</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>2.2705</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>2013-10</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>2.1886</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>2013-11</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>2.2954</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>2013-12</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>2.3455</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="n">
-        <v>2.3822</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>2014-02</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>2.3837</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>2014-03</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n">
-        <v>2.3261</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>2014-04</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>2.2328</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n">
-        <v>2.2209</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>2014-06</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>2.2355</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>2014-07</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="n">
-        <v>2.2246</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>2.268</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>2014-09</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n">
-        <v>2.3329</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>2.4483</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n">
-        <v>2.5484</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>2.6394</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>2.6342</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>2015-02</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>2.8165</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2015-03</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="n">
-        <v>3.1395</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>2015-04</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>3.0432</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2015-05</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>3.0617</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>2015-06</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>3.1117</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2015-07</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>3.2231</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="n">
-        <v>3.5143</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>2015-09</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="n">
-        <v>3.9065</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>2015-10</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="n">
-        <v>3.8801</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>2015-11</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="n">
-        <v>3.7765</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>2015-12</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="n">
-        <v>3.8711</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>2016-01</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n">
-        <v>4.0524</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>2016-02</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
-        <v>3.9737</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>2016-03</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="n">
-        <v>3.7039</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>2016-04</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="n">
-        <v>3.5658</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>2016-05</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n">
-        <v>3.5393</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>2016-06</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n">
-        <v>3.4245</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>2016-07</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n">
-        <v>3.2756</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>2016-08</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>3.2097</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>2016-09</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="n">
-        <v>3.2564</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>2016-10</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="n">
-        <v>3.1858</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2016-11</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="n">
-        <v>3.342</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>2016-12</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="n">
-        <v>3.3523</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="n">
-        <v>3.1966</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>2017-02</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="n">
-        <v>3.1042</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>2017-03</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="n">
-        <v>3.1279</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
-        <is>
-          <t>2017-04</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="n">
-        <v>3.1362</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>2017-05</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="n">
-        <v>3.2095</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>2017-06</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>3.2954</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>2017-07</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n">
-        <v>3.2061</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>2017-08</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="n">
-        <v>3.1509</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>2017-09</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="n">
-        <v>3.1348</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>2017-10</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="n">
-        <v>3.1912</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>2017-11</t>
-        </is>
-      </c>
-      <c r="B87" s="15" t="n">
-        <v>3.2594</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>2017-12</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="n">
-        <v>3.2919</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="n">
-        <v>3.2106</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>2018-02</t>
-        </is>
-      </c>
-      <c r="B90" s="16" t="n">
-        <v>3.2415</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>2018-03</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="n">
-        <v>3.2792</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>2018-04</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="n">
-        <v>3.4075</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="n">
-        <v>3.6361</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
-        <is>
-          <t>2018-06</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="n">
-        <v>3.7732</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>2018-07</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="n">
-        <v>3.8288</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>2018-08</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="n">
-        <v>3.9298</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>2018-09</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="n">
-        <v>4.1165</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
-        <is>
-          <t>2018-10</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="n">
-        <v>3.7584</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>2018-11</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="n">
-        <v>3.7867</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
-        <is>
-          <t>2018-12</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="n">
-        <v>3.8851</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t>2019-01</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="n">
-        <v>3.7417</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="13" t="inlineStr">
-        <is>
-          <t>2019-02</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="n">
-        <v>3.7236</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>2019-03</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="n">
-        <v>3.8465</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
-        <is>
-          <t>2019-04</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="n">
-        <v>3.8962</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>2019-05</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="n">
-        <v>4.0015</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>2019-06</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="n">
-        <v>3.8588</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>2019-07</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="n">
-        <v>3.7793</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="13" t="inlineStr">
-        <is>
-          <t>2019-08</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="n">
-        <v>4.1215</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="13" t="inlineStr">
-        <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n">
-        <v>4.087</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="B111" s="15" t="n">
-        <v>4.1553</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="13" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="n">
-        <v>4.1096</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>2020-01</t>
-        </is>
-      </c>
-      <c r="B113" s="15" t="n">
-        <v>4.1495</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>2020-02</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="n">
-        <v>4.341</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="n">
-        <v>4.8839</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="13" t="inlineStr">
-        <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="n">
-        <v>5.3256</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>2020-05</t>
-        </is>
-      </c>
-      <c r="B117" s="15" t="n">
-        <v>5.6434</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="13" t="inlineStr">
-        <is>
-          <t>2020-06</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="n">
-        <v>5.1966</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>2020-07</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="n">
-        <v>5.2802</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="13" t="inlineStr">
-        <is>
-          <t>2020-08</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="n">
-        <v>5.4612</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>2020-09</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="n">
-        <v>5.3995</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="13" t="inlineStr">
-        <is>
-          <t>2020-10</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="n">
-        <v>5.6258</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="n">
-        <v>5.4178</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t>2020-12</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="n">
-        <v>5.1456</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="n">
-        <v>5.3562</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="13" t="inlineStr">
-        <is>
-          <t>2021-02</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="n">
-        <v>5.4165</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>2021-03</t>
-        </is>
-      </c>
-      <c r="B127" s="15" t="n">
-        <v>5.6461</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="n">
-        <v>5.5621</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="B129" s="15" t="n">
-        <v>5.2911</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="13" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="B130" s="16" t="n">
-        <v>5.0319</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="n">
-        <v>5.1567</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="13" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="n">
-        <v>5.2517</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="B133" s="15" t="n">
-        <v>5.2797</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="13" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="n">
-        <v>5.54</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>2021-11</t>
-        </is>
-      </c>
-      <c r="B135" s="15" t="n">
-        <v>5.5569</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="13" t="inlineStr">
-        <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="n">
-        <v>5.6514</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="B137" s="15" t="n">
-        <v>5.5341</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="13" t="inlineStr">
-        <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="n">
-        <v>5.1966</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="B139" s="15" t="n">
-        <v>4.9684</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="13" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="n">
-        <v>4.758</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>2022-05</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="n">
-        <v>4.9551</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="13" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="B142" s="16" t="n">
-        <v>5.0492</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="B143" s="15" t="n">
-        <v>5.3681</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="13" t="inlineStr">
-        <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="n">
-        <v>5.1433</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="n">
-        <v>5.237</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="13" t="inlineStr">
-        <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="n">
-        <v>5.2503</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="n">
-        <v>5.2747</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="13" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="n">
-        <v>5.2424</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B149" s="15" t="n">
-        <v>5.2007</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="13" t="inlineStr">
-        <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="n">
-        <v>5.1717</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="B151" s="15" t="n">
-        <v>5.2115</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="13" t="inlineStr">
-        <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="n">
-        <v>5.0197</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="n">
-        <v>4.9828</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="13" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="B154" s="16" t="n">
-        <v>4.8516</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="n">
-        <v>4.8008</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="13" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="n">
-        <v>4.9035</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="11" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="n">
-        <v>4.937</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="13" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="B158" s="16" t="n">
-        <v>5.0648</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="n">
-        <v>4.8983</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="13" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="n">
-        <v>4.8972</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B161" s="15" t="n">
-        <v>4.9144</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="13" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B162" s="16" t="n">
-        <v>4.9644</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B163" s="15" t="n">
-        <v>4.9801</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="13" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B164" s="16" t="n">
-        <v>5.1291</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="B165" s="15" t="n">
-        <v>5.133</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="13" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="B166" s="16" t="n">
-        <v>5.389</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B167" s="15" t="n">
-        <v>5.542</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="13" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B168" s="16" t="n">
-        <v>5.5526</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="11" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B169" s="15" t="n">
-        <v>5.5416</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B170" s="16" t="n">
-        <v>5.6241</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B171" s="15" t="n">
-        <v>5.8071</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="13" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B172" s="16" t="n">
-        <v>6.097</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B173" s="15" t="n">
-        <v>6.0218</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="13" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B174" s="16" t="n">
-        <v>5.7656</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B175" s="15" t="n">
-        <v>5.7468</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="13" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B176" s="16" t="n">
-        <v>5.7837</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B177" s="15" t="n">
-        <v>5.6674</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="13" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B178" s="16" t="n">
-        <v>5.5471</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="11" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B179" s="15" t="n">
-        <v>5.5285</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="13" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B180" s="16" t="n">
-        <v>5.4469</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B181" s="15" t="n">
-        <v>5.3674</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="13" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B182" s="16" t="n">
-        <v>5.3855</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="11" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B183" s="15" t="n">
-        <v>5.3409</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="13" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B184" s="16" t="n">
-        <v>5.4531</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="11" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B185" s="15" t="n">
-        <v>5.338</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B186" s="16" t="n">
-        <v>5.2006</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="11" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B187" s="15" t="n">
-        <v>5.2316</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="13" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B188" s="16" t="n">
-        <v>5.0331</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B189" s="15" t="n">
-        <v>4.9837</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B190" s="16" t="n">
-        <v>5.1276</v>
+      <c r="B191" s="15" t="n">
+        <v>5.1139</v>
       </c>
     </row>
   </sheetData>
@@ -4803,7 +4823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6696,6 +6716,16 @@
         <v>0.16</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/projetos/relatorio-macro-excel/relatorio_macro.xlsx
+++ b/projetos/relatorio-macro-excel/relatorio_macro.xlsx
@@ -268,12 +268,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Selic'!$A$5:$A$192</f>
+              <f>'Selic'!$A$5:$A$193</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Selic'!$B$5:$B$192</f>
+              <f>'Selic'!$B$5:$B$193</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +356,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Câmbio'!$A$5:$A$191</f>
+              <f>'Câmbio'!$A$5:$A$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Câmbio'!$B$5:$B$191</f>
+              <f>'Câmbio'!$B$5:$B$192</f>
             </numRef>
           </val>
         </ser>
@@ -444,12 +444,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IPCA'!$A$5:$A$191</f>
+              <f>'IPCA'!$A$5:$A$192</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IPCA'!$B$5:$B$191</f>
+              <f>'IPCA'!$B$5:$B$192</f>
             </numRef>
           </val>
         </ser>
@@ -894,7 +894,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 01/09/2026 16:25 · Fonte: Banco Central do Brasil (API SGS)</t>
+          <t>Gerado automaticamente em 01/10/2026 18:18 · Fonte: Banco Central do Brasil (API SGS)</t>
         </is>
       </c>
     </row>
@@ -923,44 +923,44 @@
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>13,94% a.a.</t>
+          <t>13,78% a.a.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>R$ 5,1139</t>
+          <t>R$ 5,1532</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>-0,32%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>em 2026-09</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>em 2026-08</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>em 2026-07</t>
-        </is>
-      </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>até 2026-07</t>
+          <t>até 2026-08</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>em 2026-07</t>
+          <t>em 2026-08</t>
         </is>
       </c>
     </row>
@@ -978,6 +978,1941 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B193"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Taxa Selic (% a.a.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Fonte: Banco Central do Brasil — API SGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>11.91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2012-01</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>13.17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="n">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n">
+        <v>12.51</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="n">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="n">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="n">
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="n">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="n">
+        <v>11.15</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="n">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="n">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B172" s="14" t="n">
+        <v>11.77</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="n">
+        <v>12.24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B174" s="14" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="n">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B176" s="14" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="n">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B178" s="14" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B180" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B182" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B184" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B185" s="12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B186" s="14" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B188" s="14" t="n">
+        <v>14.64</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B190" s="14" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B192" s="14" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="n">
+        <v>13.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -993,7 +2928,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Taxa Selic (% a.a.)</t>
+          <t>Dólar — média mensal de venda (R$/US$)</t>
         </is>
       </c>
     </row>
@@ -1022,8 +2957,8 @@
           <t>2011-01</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>10.85</v>
+      <c r="B5" s="15" t="n">
+        <v>1.6749</v>
       </c>
     </row>
     <row r="6">
@@ -1032,8 +2967,8 @@
           <t>2011-02</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>11.17</v>
+      <c r="B6" s="16" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="7">
@@ -1042,8 +2977,8 @@
           <t>2011-03</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>11.62</v>
+      <c r="B7" s="15" t="n">
+        <v>1.6591</v>
       </c>
     </row>
     <row r="8">
@@ -1052,8 +2987,8 @@
           <t>2011-04</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>11.74</v>
+      <c r="B8" s="16" t="n">
+        <v>1.5864</v>
       </c>
     </row>
     <row r="9">
@@ -1062,8 +2997,8 @@
           <t>2011-05</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>11.92</v>
+      <c r="B9" s="15" t="n">
+        <v>1.6135</v>
       </c>
     </row>
     <row r="10">
@@ -1072,8 +3007,8 @@
           <t>2011-06</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>12.1</v>
+      <c r="B10" s="16" t="n">
+        <v>1.587</v>
       </c>
     </row>
     <row r="11">
@@ -1082,8 +3017,8 @@
           <t>2011-07</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>12.25</v>
+      <c r="B11" s="15" t="n">
+        <v>1.5639</v>
       </c>
     </row>
     <row r="12">
@@ -1092,8 +3027,8 @@
           <t>2011-08</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>12.42</v>
+      <c r="B12" s="16" t="n">
+        <v>1.597</v>
       </c>
     </row>
     <row r="13">
@@ -1102,8 +3037,8 @@
           <t>2011-09</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>11.91</v>
+      <c r="B13" s="15" t="n">
+        <v>1.7498</v>
       </c>
     </row>
     <row r="14">
@@ -1112,8 +3047,8 @@
           <t>2011-10</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>11.7</v>
+      <c r="B14" s="16" t="n">
+        <v>1.7726</v>
       </c>
     </row>
     <row r="15">
@@ -1122,8 +3057,8 @@
           <t>2011-11</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>11.4</v>
+      <c r="B15" s="15" t="n">
+        <v>1.7905</v>
       </c>
     </row>
     <row r="16">
@@ -1132,8 +3067,8 @@
           <t>2011-12</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>10.9</v>
+      <c r="B16" s="16" t="n">
+        <v>1.8369</v>
       </c>
     </row>
     <row r="17">
@@ -1142,8 +3077,8 @@
           <t>2012-01</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>10.7</v>
+      <c r="B17" s="15" t="n">
+        <v>1.7897</v>
       </c>
     </row>
     <row r="18">
@@ -1152,8 +3087,8 @@
           <t>2012-02</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>10.4</v>
+      <c r="B18" s="16" t="n">
+        <v>1.7184</v>
       </c>
     </row>
     <row r="19">
@@ -1162,8 +3097,8 @@
           <t>2012-03</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>9.82</v>
+      <c r="B19" s="15" t="n">
+        <v>1.7953</v>
       </c>
     </row>
     <row r="20">
@@ -1172,8 +3107,8 @@
           <t>2012-04</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>9.35</v>
+      <c r="B20" s="16" t="n">
+        <v>1.8548</v>
       </c>
     </row>
     <row r="21">
@@ -1182,8 +3117,8 @@
           <t>2012-05</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>8.869999999999999</v>
+      <c r="B21" s="15" t="n">
+        <v>1.986</v>
       </c>
     </row>
     <row r="22">
@@ -1192,8 +3127,8 @@
           <t>2012-06</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>8.390000000000001</v>
+      <c r="B22" s="16" t="n">
+        <v>2.0492</v>
       </c>
     </row>
     <row r="23">
@@ -1202,8 +3137,8 @@
           <t>2012-07</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>8.07</v>
+      <c r="B23" s="15" t="n">
+        <v>2.0287</v>
       </c>
     </row>
     <row r="24">
@@ -1212,8 +3147,8 @@
           <t>2012-08</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>7.85</v>
+      <c r="B24" s="16" t="n">
+        <v>2.0294</v>
       </c>
     </row>
     <row r="25">
@@ -1222,8 +3157,8 @@
           <t>2012-09</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>7.39</v>
+      <c r="B25" s="15" t="n">
+        <v>2.0281</v>
       </c>
     </row>
     <row r="26">
@@ -1232,8 +3167,8 @@
           <t>2012-10</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>7.23</v>
+      <c r="B26" s="16" t="n">
+        <v>2.0298</v>
       </c>
     </row>
     <row r="27">
@@ -1242,8 +3177,8 @@
           <t>2012-11</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>7.14</v>
+      <c r="B27" s="15" t="n">
+        <v>2.0678</v>
       </c>
     </row>
     <row r="28">
@@ -1252,8 +3187,8 @@
           <t>2012-12</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>7.16</v>
+      <c r="B28" s="16" t="n">
+        <v>2.0778</v>
       </c>
     </row>
     <row r="29">
@@ -1262,8 +3197,8 @@
           <t>2013-01</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
-        <v>7.11</v>
+      <c r="B29" s="15" t="n">
+        <v>2.0311</v>
       </c>
     </row>
     <row r="30">
@@ -1272,8 +3207,8 @@
           <t>2013-02</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>7.12</v>
+      <c r="B30" s="16" t="n">
+        <v>1.9733</v>
       </c>
     </row>
     <row r="31">
@@ -1282,8 +3217,8 @@
           <t>2013-03</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>7.15</v>
+      <c r="B31" s="15" t="n">
+        <v>1.9828</v>
       </c>
     </row>
     <row r="32">
@@ -1292,8 +3227,8 @@
           <t>2013-04</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>7.26</v>
+      <c r="B32" s="16" t="n">
+        <v>2.0022</v>
       </c>
     </row>
     <row r="33">
@@ -1302,8 +3237,8 @@
           <t>2013-05</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>7.42</v>
+      <c r="B33" s="15" t="n">
+        <v>2.0348</v>
       </c>
     </row>
     <row r="34">
@@ -1312,8 +3247,8 @@
           <t>2013-06</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>7.9</v>
+      <c r="B34" s="16" t="n">
+        <v>2.173</v>
       </c>
     </row>
     <row r="35">
@@ -1322,8 +3257,8 @@
           <t>2013-07</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>8.23</v>
+      <c r="B35" s="15" t="n">
+        <v>2.2522</v>
       </c>
     </row>
     <row r="36">
@@ -1332,8 +3267,8 @@
           <t>2013-08</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v>8.449999999999999</v>
+      <c r="B36" s="16" t="n">
+        <v>2.3422</v>
       </c>
     </row>
     <row r="37">
@@ -1342,8 +3277,8 @@
           <t>2013-09</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
-        <v>8.9</v>
+      <c r="B37" s="15" t="n">
+        <v>2.2705</v>
       </c>
     </row>
     <row r="38">
@@ -1352,8 +3287,8 @@
           <t>2013-10</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>9.25</v>
+      <c r="B38" s="16" t="n">
+        <v>2.1886</v>
       </c>
     </row>
     <row r="39">
@@ -1362,8 +3297,8 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
-        <v>9.449999999999999</v>
+      <c r="B39" s="15" t="n">
+        <v>2.2954</v>
       </c>
     </row>
     <row r="40">
@@ -1372,8 +3307,8 @@
           <t>2013-12</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v>9.9</v>
+      <c r="B40" s="16" t="n">
+        <v>2.3455</v>
       </c>
     </row>
     <row r="41">
@@ -1382,8 +3317,8 @@
           <t>2014-01</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
-        <v>10.17</v>
+      <c r="B41" s="15" t="n">
+        <v>2.3822</v>
       </c>
     </row>
     <row r="42">
@@ -1392,8 +3327,8 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>10.43</v>
+      <c r="B42" s="16" t="n">
+        <v>2.3837</v>
       </c>
     </row>
     <row r="43">
@@ -1402,8 +3337,8 @@
           <t>2014-03</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
-        <v>10.65</v>
+      <c r="B43" s="15" t="n">
+        <v>2.3261</v>
       </c>
     </row>
     <row r="44">
@@ -1412,8 +3347,8 @@
           <t>2014-04</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
-        <v>10.87</v>
+      <c r="B44" s="16" t="n">
+        <v>2.2328</v>
       </c>
     </row>
     <row r="45">
@@ -1422,8 +3357,8 @@
           <t>2014-05</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n">
-        <v>10.9</v>
+      <c r="B45" s="15" t="n">
+        <v>2.2209</v>
       </c>
     </row>
     <row r="46">
@@ -1432,8 +3367,8 @@
           <t>2014-06</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
-        <v>10.9</v>
+      <c r="B46" s="16" t="n">
+        <v>2.2355</v>
       </c>
     </row>
     <row r="47">
@@ -1442,8 +3377,8 @@
           <t>2014-07</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
-        <v>10.9</v>
+      <c r="B47" s="15" t="n">
+        <v>2.2246</v>
       </c>
     </row>
     <row r="48">
@@ -1452,8 +3387,8 @@
           <t>2014-08</t>
         </is>
       </c>
-      <c r="B48" s="14" t="n">
-        <v>10.9</v>
+      <c r="B48" s="16" t="n">
+        <v>2.268</v>
       </c>
     </row>
     <row r="49">
@@ -1462,8 +3397,8 @@
           <t>2014-09</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
-        <v>10.9</v>
+      <c r="B49" s="15" t="n">
+        <v>2.3329</v>
       </c>
     </row>
     <row r="50">
@@ -1472,8 +3407,8 @@
           <t>2014-10</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
-        <v>10.92</v>
+      <c r="B50" s="16" t="n">
+        <v>2.4483</v>
       </c>
     </row>
     <row r="51">
@@ -1482,8 +3417,8 @@
           <t>2014-11</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
-        <v>11.15</v>
+      <c r="B51" s="15" t="n">
+        <v>2.5484</v>
       </c>
     </row>
     <row r="52">
@@ -1492,8 +3427,8 @@
           <t>2014-12</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
-        <v>11.58</v>
+      <c r="B52" s="16" t="n">
+        <v>2.6394</v>
       </c>
     </row>
     <row r="53">
@@ -1502,8 +3437,8 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
-        <v>11.82</v>
+      <c r="B53" s="15" t="n">
+        <v>2.6342</v>
       </c>
     </row>
     <row r="54">
@@ -1512,8 +3447,8 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="B54" s="14" t="n">
-        <v>12.15</v>
+      <c r="B54" s="16" t="n">
+        <v>2.8165</v>
       </c>
     </row>
     <row r="55">
@@ -1522,8 +3457,8 @@
           <t>2015-03</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n">
-        <v>12.58</v>
+      <c r="B55" s="15" t="n">
+        <v>3.1395</v>
       </c>
     </row>
     <row r="56">
@@ -1532,8 +3467,8 @@
           <t>2015-04</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
-        <v>12.68</v>
+      <c r="B56" s="16" t="n">
+        <v>3.0432</v>
       </c>
     </row>
     <row r="57">
@@ -1542,8 +3477,8 @@
           <t>2015-05</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
-        <v>13.15</v>
+      <c r="B57" s="15" t="n">
+        <v>3.0617</v>
       </c>
     </row>
     <row r="58">
@@ -1552,8 +3487,8 @@
           <t>2015-06</t>
         </is>
       </c>
-      <c r="B58" s="14" t="n">
-        <v>13.58</v>
+      <c r="B58" s="16" t="n">
+        <v>3.1117</v>
       </c>
     </row>
     <row r="59">
@@ -1562,8 +3497,8 @@
           <t>2015-07</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n">
-        <v>13.69</v>
+      <c r="B59" s="15" t="n">
+        <v>3.2231</v>
       </c>
     </row>
     <row r="60">
@@ -1572,8 +3507,8 @@
           <t>2015-08</t>
         </is>
       </c>
-      <c r="B60" s="14" t="n">
-        <v>14.15</v>
+      <c r="B60" s="16" t="n">
+        <v>3.5143</v>
       </c>
     </row>
     <row r="61">
@@ -1582,8 +3517,8 @@
           <t>2015-09</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
-        <v>14.15</v>
+      <c r="B61" s="15" t="n">
+        <v>3.9065</v>
       </c>
     </row>
     <row r="62">
@@ -1592,8 +3527,8 @@
           <t>2015-10</t>
         </is>
       </c>
-      <c r="B62" s="14" t="n">
-        <v>14.15</v>
+      <c r="B62" s="16" t="n">
+        <v>3.8801</v>
       </c>
     </row>
     <row r="63">
@@ -1602,8 +3537,8 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n">
-        <v>14.15</v>
+      <c r="B63" s="15" t="n">
+        <v>3.7765</v>
       </c>
     </row>
     <row r="64">
@@ -1612,8 +3547,8 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="B64" s="14" t="n">
-        <v>14.15</v>
+      <c r="B64" s="16" t="n">
+        <v>3.8711</v>
       </c>
     </row>
     <row r="65">
@@ -1622,8 +3557,8 @@
           <t>2016-01</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
-        <v>14.15</v>
+      <c r="B65" s="15" t="n">
+        <v>4.0524</v>
       </c>
     </row>
     <row r="66">
@@ -1632,8 +3567,8 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
-        <v>14.15</v>
+      <c r="B66" s="16" t="n">
+        <v>3.9737</v>
       </c>
     </row>
     <row r="67">
@@ -1642,8 +3577,8 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n">
-        <v>14.15</v>
+      <c r="B67" s="15" t="n">
+        <v>3.7039</v>
       </c>
     </row>
     <row r="68">
@@ -1652,8 +3587,8 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
-        <v>14.15</v>
+      <c r="B68" s="16" t="n">
+        <v>3.5658</v>
       </c>
     </row>
     <row r="69">
@@ -1662,8 +3597,8 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n">
-        <v>14.15</v>
+      <c r="B69" s="15" t="n">
+        <v>3.5393</v>
       </c>
     </row>
     <row r="70">
@@ -1672,8 +3607,8 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
-        <v>14.15</v>
+      <c r="B70" s="16" t="n">
+        <v>3.4245</v>
       </c>
     </row>
     <row r="71">
@@ -1682,8 +3617,8 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="B71" s="12" t="n">
-        <v>14.15</v>
+      <c r="B71" s="15" t="n">
+        <v>3.2756</v>
       </c>
     </row>
     <row r="72">
@@ -1692,8 +3627,8 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="B72" s="14" t="n">
-        <v>14.15</v>
+      <c r="B72" s="16" t="n">
+        <v>3.2097</v>
       </c>
     </row>
     <row r="73">
@@ -1702,8 +3637,8 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
-        <v>14.15</v>
+      <c r="B73" s="15" t="n">
+        <v>3.2564</v>
       </c>
     </row>
     <row r="74">
@@ -1712,8 +3647,8 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="B74" s="14" t="n">
-        <v>14.05</v>
+      <c r="B74" s="16" t="n">
+        <v>3.1858</v>
       </c>
     </row>
     <row r="75">
@@ -1722,8 +3657,8 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
-        <v>13.9</v>
+      <c r="B75" s="15" t="n">
+        <v>3.342</v>
       </c>
     </row>
     <row r="76">
@@ -1732,8 +3667,8 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="B76" s="14" t="n">
-        <v>13.65</v>
+      <c r="B76" s="16" t="n">
+        <v>3.3523</v>
       </c>
     </row>
     <row r="77">
@@ -1742,8 +3677,8 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n">
-        <v>13.17</v>
+      <c r="B77" s="15" t="n">
+        <v>3.1966</v>
       </c>
     </row>
     <row r="78">
@@ -1752,8 +3687,8 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="B78" s="14" t="n">
-        <v>12.82</v>
+      <c r="B78" s="16" t="n">
+        <v>3.1042</v>
       </c>
     </row>
     <row r="79">
@@ -1762,8 +3697,8 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n">
-        <v>12.15</v>
+      <c r="B79" s="15" t="n">
+        <v>3.1279</v>
       </c>
     </row>
     <row r="80">
@@ -1772,8 +3707,8 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="B80" s="14" t="n">
-        <v>11.59</v>
+      <c r="B80" s="16" t="n">
+        <v>3.1362</v>
       </c>
     </row>
     <row r="81">
@@ -1782,8 +3717,8 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n">
-        <v>11.15</v>
+      <c r="B81" s="15" t="n">
+        <v>3.2095</v>
       </c>
     </row>
     <row r="82">
@@ -1792,8 +3727,8 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="B82" s="14" t="n">
-        <v>10.15</v>
+      <c r="B82" s="16" t="n">
+        <v>3.2954</v>
       </c>
     </row>
     <row r="83">
@@ -1802,8 +3737,8 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n">
-        <v>10.01</v>
+      <c r="B83" s="15" t="n">
+        <v>3.2061</v>
       </c>
     </row>
     <row r="84">
@@ -1812,8 +3747,8 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="B84" s="14" t="n">
-        <v>9.15</v>
+      <c r="B84" s="16" t="n">
+        <v>3.1509</v>
       </c>
     </row>
     <row r="85">
@@ -1822,8 +3757,8 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n">
-        <v>8.35</v>
+      <c r="B85" s="15" t="n">
+        <v>3.1348</v>
       </c>
     </row>
     <row r="86">
@@ -1832,8 +3767,8 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="B86" s="14" t="n">
-        <v>8.01</v>
+      <c r="B86" s="16" t="n">
+        <v>3.1912</v>
       </c>
     </row>
     <row r="87">
@@ -1842,8 +3777,8 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="B87" s="12" t="n">
-        <v>7.4</v>
+      <c r="B87" s="15" t="n">
+        <v>3.2594</v>
       </c>
     </row>
     <row r="88">
@@ -1852,8 +3787,8 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="B88" s="14" t="n">
-        <v>7</v>
+      <c r="B88" s="16" t="n">
+        <v>3.2919</v>
       </c>
     </row>
     <row r="89">
@@ -1862,8 +3797,8 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="B89" s="12" t="n">
-        <v>6.9</v>
+      <c r="B89" s="15" t="n">
+        <v>3.2106</v>
       </c>
     </row>
     <row r="90">
@@ -1872,8 +3807,8 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="B90" s="14" t="n">
-        <v>6.72</v>
+      <c r="B90" s="16" t="n">
+        <v>3.2415</v>
       </c>
     </row>
     <row r="91">
@@ -1882,8 +3817,8 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="B91" s="12" t="n">
-        <v>6.58</v>
+      <c r="B91" s="15" t="n">
+        <v>3.2792</v>
       </c>
     </row>
     <row r="92">
@@ -1892,8 +3827,8 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n">
-        <v>6.4</v>
+      <c r="B92" s="16" t="n">
+        <v>3.4075</v>
       </c>
     </row>
     <row r="93">
@@ -1902,8 +3837,8 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="B93" s="12" t="n">
-        <v>6.4</v>
+      <c r="B93" s="15" t="n">
+        <v>3.6361</v>
       </c>
     </row>
     <row r="94">
@@ -1912,8 +3847,8 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="B94" s="14" t="n">
-        <v>6.4</v>
+      <c r="B94" s="16" t="n">
+        <v>3.7732</v>
       </c>
     </row>
     <row r="95">
@@ -1922,8 +3857,8 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="B95" s="12" t="n">
-        <v>6.4</v>
+      <c r="B95" s="15" t="n">
+        <v>3.8288</v>
       </c>
     </row>
     <row r="96">
@@ -1932,8 +3867,8 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="B96" s="14" t="n">
-        <v>6.4</v>
+      <c r="B96" s="16" t="n">
+        <v>3.9298</v>
       </c>
     </row>
     <row r="97">
@@ -1942,8 +3877,8 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="B97" s="12" t="n">
-        <v>6.4</v>
+      <c r="B97" s="15" t="n">
+        <v>4.1165</v>
       </c>
     </row>
     <row r="98">
@@ -1952,8 +3887,8 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n">
-        <v>6.4</v>
+      <c r="B98" s="16" t="n">
+        <v>3.7584</v>
       </c>
     </row>
     <row r="99">
@@ -1962,8 +3897,8 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="B99" s="12" t="n">
-        <v>6.4</v>
+      <c r="B99" s="15" t="n">
+        <v>3.7867</v>
       </c>
     </row>
     <row r="100">
@@ -1972,8 +3907,8 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="B100" s="14" t="n">
-        <v>6.4</v>
+      <c r="B100" s="16" t="n">
+        <v>3.8851</v>
       </c>
     </row>
     <row r="101">
@@ -1982,8 +3917,8 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="B101" s="12" t="n">
-        <v>6.4</v>
+      <c r="B101" s="15" t="n">
+        <v>3.7417</v>
       </c>
     </row>
     <row r="102">
@@ -1992,8 +3927,8 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="B102" s="14" t="n">
-        <v>6.4</v>
+      <c r="B102" s="16" t="n">
+        <v>3.7236</v>
       </c>
     </row>
     <row r="103">
@@ -2002,8 +3937,8 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="B103" s="12" t="n">
-        <v>6.4</v>
+      <c r="B103" s="15" t="n">
+        <v>3.8465</v>
       </c>
     </row>
     <row r="104">
@@ -2012,8 +3947,8 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="B104" s="14" t="n">
-        <v>6.4</v>
+      <c r="B104" s="16" t="n">
+        <v>3.8962</v>
       </c>
     </row>
     <row r="105">
@@ -2022,8 +3957,8 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B105" s="12" t="n">
-        <v>6.4</v>
+      <c r="B105" s="15" t="n">
+        <v>4.0015</v>
       </c>
     </row>
     <row r="106">
@@ -2032,8 +3967,8 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
-        <v>6.4</v>
+      <c r="B106" s="16" t="n">
+        <v>3.8588</v>
       </c>
     </row>
     <row r="107">
@@ -2042,8 +3977,8 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B107" s="12" t="n">
-        <v>6.4</v>
+      <c r="B107" s="15" t="n">
+        <v>3.7793</v>
       </c>
     </row>
     <row r="108">
@@ -2052,8 +3987,8 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="B108" s="14" t="n">
-        <v>5.9</v>
+      <c r="B108" s="16" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="109">
@@ -2062,8 +3997,8 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B109" s="12" t="n">
-        <v>5.71</v>
+      <c r="B109" s="15" t="n">
+        <v>4.1215</v>
       </c>
     </row>
     <row r="110">
@@ -2072,8 +4007,8 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B110" s="14" t="n">
-        <v>5.38</v>
+      <c r="B110" s="16" t="n">
+        <v>4.087</v>
       </c>
     </row>
     <row r="111">
@@ -2082,8 +4017,8 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B111" s="12" t="n">
-        <v>4.9</v>
+      <c r="B111" s="15" t="n">
+        <v>4.1553</v>
       </c>
     </row>
     <row r="112">
@@ -2092,8 +4027,8 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="B112" s="14" t="n">
-        <v>4.59</v>
+      <c r="B112" s="16" t="n">
+        <v>4.1096</v>
       </c>
     </row>
     <row r="113">
@@ -2102,8 +4037,8 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B113" s="12" t="n">
-        <v>4.4</v>
+      <c r="B113" s="15" t="n">
+        <v>4.1495</v>
       </c>
     </row>
     <row r="114">
@@ -2112,8 +4047,8 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
-        <v>4.19</v>
+      <c r="B114" s="16" t="n">
+        <v>4.341</v>
       </c>
     </row>
     <row r="115">
@@ -2122,8 +4057,8 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B115" s="12" t="n">
-        <v>3.95</v>
+      <c r="B115" s="15" t="n">
+        <v>4.8839</v>
       </c>
     </row>
     <row r="116">
@@ -2132,8 +4067,8 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B116" s="14" t="n">
-        <v>3.65</v>
+      <c r="B116" s="16" t="n">
+        <v>5.3256</v>
       </c>
     </row>
     <row r="117">
@@ -2142,8 +4077,8 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B117" s="12" t="n">
-        <v>3.01</v>
+      <c r="B117" s="15" t="n">
+        <v>5.6434</v>
       </c>
     </row>
     <row r="118">
@@ -2152,8 +4087,8 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="B118" s="14" t="n">
-        <v>2.58</v>
+      <c r="B118" s="16" t="n">
+        <v>5.1966</v>
       </c>
     </row>
     <row r="119">
@@ -2162,8 +4097,8 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B119" s="12" t="n">
-        <v>2.15</v>
+      <c r="B119" s="15" t="n">
+        <v>5.2802</v>
       </c>
     </row>
     <row r="120">
@@ -2172,8 +4107,8 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B120" s="14" t="n">
-        <v>1.94</v>
+      <c r="B120" s="16" t="n">
+        <v>5.4612</v>
       </c>
     </row>
     <row r="121">
@@ -2182,8 +4117,8 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="B121" s="12" t="n">
-        <v>1.9</v>
+      <c r="B121" s="15" t="n">
+        <v>5.3995</v>
       </c>
     </row>
     <row r="122">
@@ -2192,8 +4127,8 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B122" s="14" t="n">
-        <v>1.9</v>
+      <c r="B122" s="16" t="n">
+        <v>5.6258</v>
       </c>
     </row>
     <row r="123">
@@ -2202,8 +4137,8 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B123" s="12" t="n">
-        <v>1.9</v>
+      <c r="B123" s="15" t="n">
+        <v>5.4178</v>
       </c>
     </row>
     <row r="124">
@@ -2212,8 +4147,8 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B124" s="14" t="n">
-        <v>1.9</v>
+      <c r="B124" s="16" t="n">
+        <v>5.1456</v>
       </c>
     </row>
     <row r="125">
@@ -2222,8 +4157,8 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B125" s="12" t="n">
-        <v>1.9</v>
+      <c r="B125" s="15" t="n">
+        <v>5.3562</v>
       </c>
     </row>
     <row r="126">
@@ -2232,8 +4167,8 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B126" s="14" t="n">
-        <v>1.9</v>
+      <c r="B126" s="16" t="n">
+        <v>5.4165</v>
       </c>
     </row>
     <row r="127">
@@ -2242,8 +4177,8 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B127" s="12" t="n">
-        <v>2.23</v>
+      <c r="B127" s="15" t="n">
+        <v>5.6461</v>
       </c>
     </row>
     <row r="128">
@@ -2252,8 +4187,8 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B128" s="14" t="n">
-        <v>2.65</v>
+      <c r="B128" s="16" t="n">
+        <v>5.5621</v>
       </c>
     </row>
     <row r="129">
@@ -2262,8 +4197,8 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B129" s="12" t="n">
-        <v>3.29</v>
+      <c r="B129" s="15" t="n">
+        <v>5.2911</v>
       </c>
     </row>
     <row r="130">
@@ -2272,8 +4207,8 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B130" s="14" t="n">
-        <v>3.76</v>
+      <c r="B130" s="16" t="n">
+        <v>5.0319</v>
       </c>
     </row>
     <row r="131">
@@ -2282,8 +4217,8 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="B131" s="12" t="n">
-        <v>4.15</v>
+      <c r="B131" s="15" t="n">
+        <v>5.1567</v>
       </c>
     </row>
     <row r="132">
@@ -2292,8 +4227,8 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B132" s="14" t="n">
-        <v>5.01</v>
+      <c r="B132" s="16" t="n">
+        <v>5.2517</v>
       </c>
     </row>
     <row r="133">
@@ -2302,8 +4237,8 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B133" s="12" t="n">
-        <v>5.43</v>
+      <c r="B133" s="15" t="n">
+        <v>5.2797</v>
       </c>
     </row>
     <row r="134">
@@ -2312,8 +4247,8 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B134" s="14" t="n">
-        <v>6.3</v>
+      <c r="B134" s="16" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="135">
@@ -2322,8 +4257,8 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B135" s="12" t="n">
-        <v>7.65</v>
+      <c r="B135" s="15" t="n">
+        <v>5.5569</v>
       </c>
     </row>
     <row r="136">
@@ -2332,8 +4267,8 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B136" s="14" t="n">
-        <v>8.76</v>
+      <c r="B136" s="16" t="n">
+        <v>5.6514</v>
       </c>
     </row>
     <row r="137">
@@ -2342,8 +4277,8 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B137" s="12" t="n">
-        <v>9.15</v>
+      <c r="B137" s="15" t="n">
+        <v>5.5341</v>
       </c>
     </row>
     <row r="138">
@@ -2352,8 +4287,8 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B138" s="14" t="n">
-        <v>10.49</v>
+      <c r="B138" s="16" t="n">
+        <v>5.1966</v>
       </c>
     </row>
     <row r="139">
@@ -2362,8 +4297,8 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="B139" s="12" t="n">
-        <v>11.15</v>
+      <c r="B139" s="15" t="n">
+        <v>4.9684</v>
       </c>
     </row>
     <row r="140">
@@ -2372,8 +4307,8 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="B140" s="14" t="n">
-        <v>11.65</v>
+      <c r="B140" s="16" t="n">
+        <v>4.758</v>
       </c>
     </row>
     <row r="141">
@@ -2382,8 +4317,8 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="B141" s="12" t="n">
-        <v>12.51</v>
+      <c r="B141" s="15" t="n">
+        <v>4.9551</v>
       </c>
     </row>
     <row r="142">
@@ -2392,8 +4327,8 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="B142" s="14" t="n">
-        <v>12.89</v>
+      <c r="B142" s="16" t="n">
+        <v>5.0492</v>
       </c>
     </row>
     <row r="143">
@@ -2402,8 +4337,8 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="B143" s="12" t="n">
-        <v>13.15</v>
+      <c r="B143" s="15" t="n">
+        <v>5.3681</v>
       </c>
     </row>
     <row r="144">
@@ -2412,8 +4347,8 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="B144" s="14" t="n">
-        <v>13.58</v>
+      <c r="B144" s="16" t="n">
+        <v>5.1433</v>
       </c>
     </row>
     <row r="145">
@@ -2422,8 +4357,8 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="B145" s="12" t="n">
-        <v>13.65</v>
+      <c r="B145" s="15" t="n">
+        <v>5.237</v>
       </c>
     </row>
     <row r="146">
@@ -2432,8 +4367,8 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="B146" s="14" t="n">
-        <v>13.65</v>
+      <c r="B146" s="16" t="n">
+        <v>5.2503</v>
       </c>
     </row>
     <row r="147">
@@ -2442,8 +4377,8 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="B147" s="12" t="n">
-        <v>13.65</v>
+      <c r="B147" s="15" t="n">
+        <v>5.2747</v>
       </c>
     </row>
     <row r="148">
@@ -2452,8 +4387,8 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="B148" s="14" t="n">
-        <v>13.65</v>
+      <c r="B148" s="16" t="n">
+        <v>5.2424</v>
       </c>
     </row>
     <row r="149">
@@ -2462,8 +4397,8 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="B149" s="12" t="n">
-        <v>13.65</v>
+      <c r="B149" s="15" t="n">
+        <v>5.2007</v>
       </c>
     </row>
     <row r="150">
@@ -2472,8 +4407,8 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="B150" s="14" t="n">
-        <v>13.65</v>
+      <c r="B150" s="16" t="n">
+        <v>5.1717</v>
       </c>
     </row>
     <row r="151">
@@ -2482,8 +4417,8 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="B151" s="12" t="n">
-        <v>13.65</v>
+      <c r="B151" s="15" t="n">
+        <v>5.2115</v>
       </c>
     </row>
     <row r="152">
@@ -2492,8 +4427,8 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="B152" s="14" t="n">
-        <v>13.65</v>
+      <c r="B152" s="16" t="n">
+        <v>5.0197</v>
       </c>
     </row>
     <row r="153">
@@ -2502,8 +4437,8 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="B153" s="12" t="n">
-        <v>13.65</v>
+      <c r="B153" s="15" t="n">
+        <v>4.9828</v>
       </c>
     </row>
     <row r="154">
@@ -2512,8 +4447,8 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="B154" s="14" t="n">
-        <v>13.65</v>
+      <c r="B154" s="16" t="n">
+        <v>4.8516</v>
       </c>
     </row>
     <row r="155">
@@ -2522,8 +4457,8 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="B155" s="12" t="n">
-        <v>13.65</v>
+      <c r="B155" s="15" t="n">
+        <v>4.8008</v>
       </c>
     </row>
     <row r="156">
@@ -2532,8 +4467,8 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="B156" s="14" t="n">
-        <v>13.19</v>
+      <c r="B156" s="16" t="n">
+        <v>4.9035</v>
       </c>
     </row>
     <row r="157">
@@ -2542,8 +4477,8 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="B157" s="12" t="n">
-        <v>12.97</v>
+      <c r="B157" s="15" t="n">
+        <v>4.937</v>
       </c>
     </row>
     <row r="158">
@@ -2552,8 +4487,8 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="B158" s="14" t="n">
-        <v>12.65</v>
+      <c r="B158" s="16" t="n">
+        <v>5.0648</v>
       </c>
     </row>
     <row r="159">
@@ -2562,8 +4497,8 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="B159" s="12" t="n">
-        <v>12.17</v>
+      <c r="B159" s="15" t="n">
+        <v>4.8983</v>
       </c>
     </row>
     <row r="160">
@@ -2572,8 +4507,8 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="B160" s="14" t="n">
-        <v>11.87</v>
+      <c r="B160" s="16" t="n">
+        <v>4.8972</v>
       </c>
     </row>
     <row r="161">
@@ -2582,8 +4517,8 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="B161" s="12" t="n">
-        <v>11.65</v>
+      <c r="B161" s="15" t="n">
+        <v>4.9144</v>
       </c>
     </row>
     <row r="162">
@@ -2592,8 +4527,8 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="B162" s="14" t="n">
-        <v>11.15</v>
+      <c r="B162" s="16" t="n">
+        <v>4.9644</v>
       </c>
     </row>
     <row r="163">
@@ -2602,8 +4537,8 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="B163" s="12" t="n">
-        <v>11</v>
+      <c r="B163" s="15" t="n">
+        <v>4.9801</v>
       </c>
     </row>
     <row r="164">
@@ -2612,8 +4547,8 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="B164" s="14" t="n">
-        <v>10.65</v>
+      <c r="B164" s="16" t="n">
+        <v>5.1291</v>
       </c>
     </row>
     <row r="165">
@@ -2622,8 +4557,8 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="B165" s="12" t="n">
-        <v>10.46</v>
+      <c r="B165" s="15" t="n">
+        <v>5.133</v>
       </c>
     </row>
     <row r="166">
@@ -2632,8 +4567,8 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="B166" s="14" t="n">
-        <v>10.4</v>
+      <c r="B166" s="16" t="n">
+        <v>5.389</v>
       </c>
     </row>
     <row r="167">
@@ -2642,8 +4577,8 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="B167" s="12" t="n">
-        <v>10.4</v>
+      <c r="B167" s="15" t="n">
+        <v>5.542</v>
       </c>
     </row>
     <row r="168">
@@ -2652,8 +4587,8 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="B168" s="14" t="n">
-        <v>10.4</v>
+      <c r="B168" s="16" t="n">
+        <v>5.5526</v>
       </c>
     </row>
     <row r="169">
@@ -2662,8 +4597,8 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B169" s="12" t="n">
-        <v>10.5</v>
+      <c r="B169" s="15" t="n">
+        <v>5.5416</v>
       </c>
     </row>
     <row r="170">
@@ -2672,8 +4607,8 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="B170" s="14" t="n">
-        <v>10.65</v>
+      <c r="B170" s="16" t="n">
+        <v>5.6241</v>
       </c>
     </row>
     <row r="171">
@@ -2682,8 +4617,8 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="B171" s="12" t="n">
-        <v>11.04</v>
+      <c r="B171" s="15" t="n">
+        <v>5.8071</v>
       </c>
     </row>
     <row r="172">
@@ -2692,8 +4627,8 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="B172" s="14" t="n">
-        <v>11.77</v>
+      <c r="B172" s="16" t="n">
+        <v>6.097</v>
       </c>
     </row>
     <row r="173">
@@ -2702,8 +4637,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B173" s="12" t="n">
-        <v>12.24</v>
+      <c r="B173" s="15" t="n">
+        <v>6.0218</v>
       </c>
     </row>
     <row r="174">
@@ -2712,8 +4647,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B174" s="14" t="n">
-        <v>13.15</v>
+      <c r="B174" s="16" t="n">
+        <v>5.7656</v>
       </c>
     </row>
     <row r="175">
@@ -2722,8 +4657,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B175" s="12" t="n">
-        <v>13.57</v>
+      <c r="B175" s="15" t="n">
+        <v>5.7468</v>
       </c>
     </row>
     <row r="176">
@@ -2732,8 +4667,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B176" s="14" t="n">
-        <v>14.15</v>
+      <c r="B176" s="16" t="n">
+        <v>5.7837</v>
       </c>
     </row>
     <row r="177">
@@ -2742,8 +4677,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B177" s="12" t="n">
-        <v>14.55</v>
+      <c r="B177" s="15" t="n">
+        <v>5.6674</v>
       </c>
     </row>
     <row r="178">
@@ -2752,8 +4687,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B178" s="14" t="n">
-        <v>14.74</v>
+      <c r="B178" s="16" t="n">
+        <v>5.5471</v>
       </c>
     </row>
     <row r="179">
@@ -2762,8 +4697,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B179" s="12" t="n">
-        <v>14.9</v>
+      <c r="B179" s="15" t="n">
+        <v>5.5285</v>
       </c>
     </row>
     <row r="180">
@@ -2772,8 +4707,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B180" s="14" t="n">
-        <v>14.9</v>
+      <c r="B180" s="16" t="n">
+        <v>5.4469</v>
       </c>
     </row>
     <row r="181">
@@ -2782,8 +4717,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B181" s="12" t="n">
-        <v>14.9</v>
+      <c r="B181" s="15" t="n">
+        <v>5.3674</v>
       </c>
     </row>
     <row r="182">
@@ -2792,8 +4727,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B182" s="14" t="n">
-        <v>14.9</v>
+      <c r="B182" s="16" t="n">
+        <v>5.3855</v>
       </c>
     </row>
     <row r="183">
@@ -2802,8 +4737,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B183" s="12" t="n">
-        <v>14.9</v>
+      <c r="B183" s="15" t="n">
+        <v>5.3409</v>
       </c>
     </row>
     <row r="184">
@@ -2812,8 +4747,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B184" s="14" t="n">
-        <v>14.9</v>
+      <c r="B184" s="16" t="n">
+        <v>5.4531</v>
       </c>
     </row>
     <row r="185">
@@ -2822,8 +4757,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B185" s="12" t="n">
-        <v>14.9</v>
+      <c r="B185" s="15" t="n">
+        <v>5.338</v>
       </c>
     </row>
     <row r="186">
@@ -2832,8 +4767,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B186" s="14" t="n">
-        <v>14.9</v>
+      <c r="B186" s="16" t="n">
+        <v>5.2006</v>
       </c>
     </row>
     <row r="187">
@@ -2842,8 +4777,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B187" s="12" t="n">
-        <v>14.8</v>
+      <c r="B187" s="15" t="n">
+        <v>5.2316</v>
       </c>
     </row>
     <row r="188">
@@ -2852,8 +4787,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B188" s="14" t="n">
-        <v>14.64</v>
+      <c r="B188" s="16" t="n">
+        <v>5.0331</v>
       </c>
     </row>
     <row r="189">
@@ -2862,8 +4797,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B189" s="12" t="n">
-        <v>14.4</v>
+      <c r="B189" s="15" t="n">
+        <v>4.9837</v>
       </c>
     </row>
     <row r="190">
@@ -2872,8 +4807,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B190" s="14" t="n">
-        <v>14.29</v>
+      <c r="B190" s="16" t="n">
+        <v>5.1276</v>
       </c>
     </row>
     <row r="191">
@@ -2882,8 +4817,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B191" s="12" t="n">
-        <v>14.15</v>
+      <c r="B191" s="15" t="n">
+        <v>5.1139</v>
       </c>
     </row>
     <row r="192">
@@ -2892,1923 +4827,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B192" s="14" t="n">
-        <v>13.94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B191"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Dólar — média mensal de venda (R$/US$)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Fonte: Banco Central do Brasil — API SGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Mês</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>2011-01</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>1.6749</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>2011-02</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>1.668</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>2011-03</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>1.6591</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>2011-04</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>1.5864</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>2011-05</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>1.6135</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>2011-06</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>1.587</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>2011-07</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>1.5639</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2011-08</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>1.597</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>2011-09</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>1.7498</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1.7726</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>2011-11</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>1.7905</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>2011-12</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>1.8369</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>2012-01</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>1.7897</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>2012-02</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>1.7184</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>2012-03</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>1.7953</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>2012-04</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>1.8548</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>2012-05</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>1.986</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>2012-06</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>2.0492</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2012-07</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>2.0287</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>2012-08</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>2.0294</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>2012-09</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>2.0281</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>2012-10</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>2.0298</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>2012-11</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>2.0678</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>2012-12</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>2.0778</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>2013-01</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>2.0311</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>2013-02</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>1.9733</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>2013-03</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>1.9828</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>2.0022</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>2013-05</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>2.0348</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>2013-06</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
-        <v>2.173</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>2013-07</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>2.2522</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>2013-08</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>2.3422</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>2013-09</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>2.2705</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>2013-10</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>2.1886</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>2013-11</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>2.2954</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>2013-12</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>2.3455</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="n">
-        <v>2.3822</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>2014-02</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>2.3837</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>2014-03</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n">
-        <v>2.3261</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>2014-04</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>2.2328</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n">
-        <v>2.2209</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>2014-06</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>2.2355</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>2014-07</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="n">
-        <v>2.2246</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>2.268</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>2014-09</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n">
-        <v>2.3329</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>2014-10</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>2.4483</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>2014-11</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n">
-        <v>2.5484</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n">
-        <v>2.6394</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>2.6342</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>2015-02</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>2.8165</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>2015-03</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="n">
-        <v>3.1395</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>2015-04</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>3.0432</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>2015-05</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>3.0617</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>2015-06</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>3.1117</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>2015-07</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>3.2231</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="n">
-        <v>3.5143</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>2015-09</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="n">
-        <v>3.9065</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>2015-10</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="n">
-        <v>3.8801</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>2015-11</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="n">
-        <v>3.7765</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>2015-12</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="n">
-        <v>3.8711</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>2016-01</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n">
-        <v>4.0524</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>2016-02</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
-        <v>3.9737</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>2016-03</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="n">
-        <v>3.7039</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>2016-04</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="n">
-        <v>3.5658</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>2016-05</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n">
-        <v>3.5393</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>2016-06</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n">
-        <v>3.4245</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>2016-07</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n">
-        <v>3.2756</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>2016-08</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>3.2097</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>2016-09</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="n">
-        <v>3.2564</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>2016-10</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="n">
-        <v>3.1858</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2016-11</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="n">
-        <v>3.342</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>2016-12</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="n">
-        <v>3.3523</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="n">
-        <v>3.1966</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>2017-02</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="n">
-        <v>3.1042</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>2017-03</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="n">
-        <v>3.1279</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
-        <is>
-          <t>2017-04</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="n">
-        <v>3.1362</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>2017-05</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="n">
-        <v>3.2095</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>2017-06</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>3.2954</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>2017-07</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n">
-        <v>3.2061</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>2017-08</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="n">
-        <v>3.1509</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>2017-09</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="n">
-        <v>3.1348</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>2017-10</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="n">
-        <v>3.1912</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>2017-11</t>
-        </is>
-      </c>
-      <c r="B87" s="15" t="n">
-        <v>3.2594</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>2017-12</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="n">
-        <v>3.2919</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="n">
-        <v>3.2106</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>2018-02</t>
-        </is>
-      </c>
-      <c r="B90" s="16" t="n">
-        <v>3.2415</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>2018-03</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="n">
-        <v>3.2792</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>2018-04</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="n">
-        <v>3.4075</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="n">
-        <v>3.6361</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
-        <is>
-          <t>2018-06</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="n">
-        <v>3.7732</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>2018-07</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="n">
-        <v>3.8288</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>2018-08</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="n">
-        <v>3.9298</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>2018-09</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="n">
-        <v>4.1165</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
-        <is>
-          <t>2018-10</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="n">
-        <v>3.7584</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>2018-11</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="n">
-        <v>3.7867</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
-        <is>
-          <t>2018-12</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="n">
-        <v>3.8851</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t>2019-01</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="n">
-        <v>3.7417</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="13" t="inlineStr">
-        <is>
-          <t>2019-02</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="n">
-        <v>3.7236</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>2019-03</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="n">
-        <v>3.8465</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
-        <is>
-          <t>2019-04</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="n">
-        <v>3.8962</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>2019-05</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="n">
-        <v>4.0015</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>2019-06</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="n">
-        <v>3.8588</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>2019-07</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="n">
-        <v>3.7793</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="13" t="inlineStr">
-        <is>
-          <t>2019-08</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="n">
-        <v>4.1215</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="13" t="inlineStr">
-        <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n">
-        <v>4.087</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="B111" s="15" t="n">
-        <v>4.1553</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="13" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="n">
-        <v>4.1096</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>2020-01</t>
-        </is>
-      </c>
-      <c r="B113" s="15" t="n">
-        <v>4.1495</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>2020-02</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="n">
-        <v>4.341</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="n">
-        <v>4.8839</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="13" t="inlineStr">
-        <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="n">
-        <v>5.3256</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>2020-05</t>
-        </is>
-      </c>
-      <c r="B117" s="15" t="n">
-        <v>5.6434</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="13" t="inlineStr">
-        <is>
-          <t>2020-06</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="n">
-        <v>5.1966</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>2020-07</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="n">
-        <v>5.2802</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="13" t="inlineStr">
-        <is>
-          <t>2020-08</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="n">
-        <v>5.4612</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>2020-09</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="n">
-        <v>5.3995</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="13" t="inlineStr">
-        <is>
-          <t>2020-10</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="n">
-        <v>5.6258</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="n">
-        <v>5.4178</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t>2020-12</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="n">
-        <v>5.1456</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="n">
-        <v>5.3562</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="13" t="inlineStr">
-        <is>
-          <t>2021-02</t>
-        </is>
-      </c>
-      <c r="B126" s="16" t="n">
-        <v>5.4165</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>2021-03</t>
-        </is>
-      </c>
-      <c r="B127" s="15" t="n">
-        <v>5.6461</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="n">
-        <v>5.5621</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="B129" s="15" t="n">
-        <v>5.2911</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="13" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="B130" s="16" t="n">
-        <v>5.0319</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="n">
-        <v>5.1567</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="13" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="n">
-        <v>5.2517</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="B133" s="15" t="n">
-        <v>5.2797</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="13" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="n">
-        <v>5.54</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>2021-11</t>
-        </is>
-      </c>
-      <c r="B135" s="15" t="n">
-        <v>5.5569</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="13" t="inlineStr">
-        <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="n">
-        <v>5.6514</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="B137" s="15" t="n">
-        <v>5.5341</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="13" t="inlineStr">
-        <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="n">
-        <v>5.1966</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="B139" s="15" t="n">
-        <v>4.9684</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="13" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="n">
-        <v>4.758</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>2022-05</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="n">
-        <v>4.9551</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="13" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="B142" s="16" t="n">
-        <v>5.0492</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="B143" s="15" t="n">
-        <v>5.3681</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="13" t="inlineStr">
-        <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="n">
-        <v>5.1433</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="n">
-        <v>5.237</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="13" t="inlineStr">
-        <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="n">
-        <v>5.2503</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="11" t="inlineStr">
-        <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="n">
-        <v>5.2747</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="13" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="n">
-        <v>5.2424</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B149" s="15" t="n">
-        <v>5.2007</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="13" t="inlineStr">
-        <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="n">
-        <v>5.1717</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="B151" s="15" t="n">
-        <v>5.2115</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="13" t="inlineStr">
-        <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="n">
-        <v>5.0197</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="n">
-        <v>4.9828</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="13" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="B154" s="16" t="n">
-        <v>4.8516</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="n">
-        <v>4.8008</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="13" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="n">
-        <v>4.9035</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="11" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="n">
-        <v>4.937</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="13" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="B158" s="16" t="n">
-        <v>5.0648</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="n">
-        <v>4.8983</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="13" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="n">
-        <v>4.8972</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="11" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B161" s="15" t="n">
-        <v>4.9144</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="13" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B162" s="16" t="n">
-        <v>4.9644</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B163" s="15" t="n">
-        <v>4.9801</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="13" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B164" s="16" t="n">
-        <v>5.1291</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="11" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="B165" s="15" t="n">
-        <v>5.133</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="13" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="B166" s="16" t="n">
-        <v>5.389</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B167" s="15" t="n">
-        <v>5.542</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="13" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B168" s="16" t="n">
-        <v>5.5526</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="11" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B169" s="15" t="n">
-        <v>5.5416</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B170" s="16" t="n">
-        <v>5.6241</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="11" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B171" s="15" t="n">
-        <v>5.8071</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="13" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B172" s="16" t="n">
-        <v>6.097</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B173" s="15" t="n">
-        <v>6.0218</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="13" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B174" s="16" t="n">
-        <v>5.7656</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B175" s="15" t="n">
-        <v>5.7468</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="13" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B176" s="16" t="n">
-        <v>5.7837</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B177" s="15" t="n">
-        <v>5.6674</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="13" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B178" s="16" t="n">
-        <v>5.5471</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="11" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B179" s="15" t="n">
-        <v>5.5285</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="13" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B180" s="16" t="n">
-        <v>5.4469</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B181" s="15" t="n">
-        <v>5.3674</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="13" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B182" s="16" t="n">
-        <v>5.3855</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="11" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B183" s="15" t="n">
-        <v>5.3409</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="13" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B184" s="16" t="n">
-        <v>5.4531</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="11" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B185" s="15" t="n">
-        <v>5.338</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B186" s="16" t="n">
-        <v>5.2006</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="11" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B187" s="15" t="n">
-        <v>5.2316</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="13" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B188" s="16" t="n">
-        <v>5.0331</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B189" s="15" t="n">
-        <v>4.9837</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B190" s="16" t="n">
-        <v>5.1276</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="11" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B191" s="15" t="n">
-        <v>5.1139</v>
+      <c r="B192" s="16" t="n">
+        <v>5.1532</v>
       </c>
     </row>
   </sheetData>
@@ -4823,7 +4843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B191"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6726,6 +6746,16 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B192" s="14" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
